--- a/_qa/Model_Tests.xlsx
+++ b/_qa/Model_Tests.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="648">
   <si>
     <t>Test ID</t>
   </si>
@@ -1253,19 +1253,1768 @@
   </si>
   <si>
     <t>No element count errors shown</t>
+  </si>
+  <si>
+    <t>Navigate to Basic Settings tab</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel (the main Quodsi panel, not an element editor)
+3. The Model Panel should be visible on the right side</t>
+  </si>
+  <si>
+    <t>1. Look at the top of the Model Panel - you'll see 6 small tab icons
+2. Find the gear icon (first tab) - this is the Basic Settings tab
+3. Click on the gear icon
+4. Observe what content appears in the panel below the tabs</t>
+  </si>
+  <si>
+    <t>1. The gear icon should appear highlighted or selected
+2. The panel below shows Basic Settings content:
+   - A 'Model Name' text box near the top
+   - Run Time settings (if in Clock mode)
+   - An 'Advanced Settings' collapsible section
+3. This is where you configure overall model parameters</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. The Model Panel is open
+3. Currently on any other tab</t>
+  </si>
+  <si>
+    <t>1. Look at the tab icons at the top of the Model Panel
+2. Find the States tab icon (second tab from left)
+3. Click on the States tab icon
+4. Observe what content appears in the panel</t>
+  </si>
+  <si>
+    <t>1. The States tab icon should now appear highlighted
+2. The panel below shows the States editor:
+   - A list of model-level states (may be empty)
+   - An 'Add State' or '+' button to create new states
+3. NOTE: States here are MODEL-level states, different from entity states
+4. Changes auto-save (no Save button needed)</t>
+  </si>
+  <si>
+    <t>1. Look at the tab icons at the top of the Model Panel
+2. Find the Requirements tab icon (third tab from left)
+3. Click on the Requirements tab icon
+4. Observe what content appears in the panel</t>
+  </si>
+  <si>
+    <t>1. The Requirements tab icon should now appear highlighted
+2. The panel below shows the Resource Requirements manager:
+   - A list of resource requirements (may include auto-generated ones)
+   - An 'Add' button to create new requirements
+3. Requirements define which resources are needed for activities
+4. Changes auto-save when using the modal dialogs</t>
+  </si>
+  <si>
+    <t>1. Look at the tab icons at the top of the Model Panel
+2. Find the Scenarios tab icon (fourth tab from left)
+3. Click on the Scenarios tab icon
+4. Observe what content appears in the panel</t>
+  </si>
+  <si>
+    <t>1. The Scenarios tab icon should now appear highlighted
+2. The panel below shows the Scenarios panel:
+   - A list of simulation scenarios
+   - Options to create, edit, or delete scenarios
+3. Scenarios allow running multiple simulation variations
+4. Changes auto-save</t>
+  </si>
+  <si>
+    <t>1. Look at the tab icons at the top of the Model Panel
+2. Find the Validation tab icon (fifth tab from left)
+3. Click on the Validation tab icon
+4. Observe what content appears in the panel</t>
+  </si>
+  <si>
+    <t>1. The Validation tab icon should now appear highlighted
+2. The panel below shows the Validation dashboard:
+   - A list of errors (red) if any exist
+   - A list of warnings (yellow/orange) if any exist
+   - A success message if the model is valid
+3. Validation runs automatically when you open this tab
+4. Click on any error/warning to navigate to that element</t>
+  </si>
+  <si>
+    <t>1. Look at the tab icons at the top of the Model Panel
+2. Find the Utilities tab icon (sixth/last tab from left)
+3. Click on the Utilities tab icon
+4. Observe what content appears in the panel</t>
+  </si>
+  <si>
+    <t>1. The Utilities tab icon should now appear highlighted
+2. The panel below shows the Utilities panel:
+   - A 'Diagnostics' section
+   - A 'View Model JSON' button for debugging
+3. This tab provides diagnostic and troubleshooting tools
+4. Useful for developers or advanced users</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. The Model Panel is open</t>
+  </si>
+  <si>
+    <t>1. Look at the top of the Model Panel
+2. Count the number of tab icons visible
+3. Identify each tab by its icon (left to right):
+   - Tab 1: Gear icon (Basic Settings)
+   - Tab 2: States icon
+   - Tab 3: Requirements icon
+   - Tab 4: Scenarios icon
+   - Tab 5: Validation icon (may show error count badge)
+   - Tab 6: Utilities icon
+4. Note the position and spacing of all tabs</t>
+  </si>
+  <si>
+    <t>1. Exactly 6 tab icons should be visible at the top of the panel
+2. All icons should be clearly distinguishable
+3. The tabs should be evenly spaced and aligned
+4. One tab should appear selected/highlighted
+5. The Validation tab may show a badge with error/warning count</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. The Model Panel is open
+3. All 6 tab icons are visible</t>
+  </si>
+  <si>
+    <t>1. Move your mouse cursor over the first tab icon (gear icon)
+2. Hold your mouse still for 1-2 seconds without clicking
+3. Observe if a tooltip appears
+4. Repeat for each of the other 5 tab icons:
+   - States tab
+   - Requirements tab
+   - Scenarios tab
+   - Validation tab
+   - Utilities tab
+5. Note the tooltip text for each</t>
+  </si>
+  <si>
+    <t>1. Each tab should show a tooltip when hovered:
+   - Gear icon: 'Basic Settings' or similar
+   - States: 'States' or 'Model States'
+   - Requirements: 'Resource Requirements' or similar
+   - Scenarios: 'Scenarios'
+   - Validation: 'Validation' or 'Model Validation'
+   - Utilities: 'Utilities' or 'Diagnostics'
+2. Tooltips appear after 1-2 seconds of hovering
+3. Tooltips disappear when mouse moves away</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel
+3. Click the Basic Settings tab (gear icon, first tab)
+4. Note the current model name displayed</t>
+  </si>
+  <si>
+    <t>1. Find the 'Model Name' text box near the top of the panel
+2. Click inside the text box - you should see a blinking cursor
+3. Select all existing text (Ctrl+A or triple-click)
+4. Type a new name, for example: 'Customer Service Simulation'
+5. Press Tab or click somewhere outside the text box</t>
+  </si>
+  <si>
+    <t>1. The text box now displays your new name 'Customer Service Simulation'
+2. Look at the bottom of the panel
+3. The Save button (blue) should now be ENABLED (not grayed out)
+4. The Cancel button should also appear next to Save
+5. This indicates you have unsaved changes</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Basic Settings tab
+3. The model is in 'Clock' time mode (not Calendar Date mode)
+4. You can see a 'Run Time' section with a numeric field</t>
+  </si>
+  <si>
+    <t>1. Find the 'Run Time' numeric field (shows how long the simulation will run)
+2. Click inside the field
+3. Select all existing text
+4. Type: 100
+5. Press Tab or click outside the field
+6. Observe the value and the Save button</t>
+  </si>
+  <si>
+    <t>1. The Run Time field now shows 100
+2. The Save button should become enabled (blue)
+3. This sets the simulation to run for 100 time units
+4. The actual duration depends on the time unit selected (hours, days, etc.)
+5. Changes require clicking Save to persist</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Basic Settings tab
+3. The model is in 'Clock' time mode
+4. You can see a 'Run Time' section with a unit dropdown</t>
+  </si>
+  <si>
+    <t>1. Find the Run Time unit dropdown (next to the numeric field)
+   - May show 'Hours', 'Minutes', or another time unit
+2. Click on the dropdown to open it
+3. You should see options like: Seconds, Minutes, Hours, Days
+4. Select 'Days' from the dropdown
+5. Observe the change</t>
+  </si>
+  <si>
+    <t>1. The dropdown now shows 'Days' as the selected unit
+2. The Save button should become enabled
+3. This means the Run Time value will be interpreted as days
+   - If Run Time is 100, the simulation runs for 100 days
+4. Click Save to persist the change</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Basic Settings tab
+3. The model is in 'CalendarDate' time mode (check Advanced Settings)</t>
+  </si>
+  <si>
+    <t>1. Look at the Basic Settings panel content
+2. Search for the 'Run Time' section that you would see in Clock mode
+3. Specifically look for:
+   - A 'Run Time' label with numeric input
+   - A time unit dropdown (Hours, Days, etc.)
+4. Note whether these fields are visible or hidden</t>
+  </si>
+  <si>
+    <t>1. The 'Run Time' fields should NOT be visible in Calendar Date mode
+2. Instead, you should see date fields:
+   - Start Date
+   - Finish Date
+   - Possibly Warmup Date
+3. In Calendar mode, duration is determined by the date range, not a run time value
+4. This is the expected behavior - not a bug</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Basic Settings tab
+3. Look for an 'Advanced Settings' section (may be collapsed)</t>
+  </si>
+  <si>
+    <t>1. Find the 'Advanced Settings' section in the Basic Settings panel
+   - It should have an arrow or expand/collapse icon
+   - The section header should be clickable
+2. If the section is collapsed (arrow pointing right or down):
+   - Click on the 'Advanced Settings' header or arrow
+3. Observe what happens to the section</t>
+  </si>
+  <si>
+    <t>1. The Advanced Settings section should EXPAND
+2. The arrow/icon should change to indicate expanded state
+3. You should now see additional fields including:
+   - Replications (number of simulation runs)
+   - Time Mode dropdown (Clock vs CalendarDate)
+   - Clock Unit (if in Clock mode)
+   - Warmup Time or Warmup Date
+   - Random Seed
+4. These are advanced configuration options</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Basic Settings tab
+3. The 'Advanced Settings' section is currently EXPANDED</t>
+  </si>
+  <si>
+    <t>1. Find the 'Advanced Settings' section header
+2. The section should be showing all the advanced fields
+3. Click on the 'Advanced Settings' header or the collapse arrow
+4. Observe what happens to the section</t>
+  </si>
+  <si>
+    <t>1. The Advanced Settings section should COLLAPSE
+2. The arrow/icon should change to indicate collapsed state
+3. The advanced fields should now be hidden:
+   - Replications, Time Mode, Clock Unit, etc. are no longer visible
+4. Only the section header remains visible
+5. Click again to expand if needed</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Basic Settings tab
+3. Expand the 'Advanced Settings' section
+4. Find the 'Replications' field</t>
+  </si>
+  <si>
+    <t>1. Locate the 'Replications' numeric field in Advanced Settings
+   - This controls how many times the simulation runs
+2. Click inside the field
+3. Select all existing text
+4. Type: 10
+5. Press Tab or click outside the field</t>
+  </si>
+  <si>
+    <t>1. The Replications field now shows 10
+2. The Save button should become enabled
+3. This means the simulation will run 10 times (replications)
+4. Multiple replications help account for randomness in simulations
+5. Click Save to persist the change</t>
+  </si>
+  <si>
+    <t>1. Locate the 'Replications' numeric field
+2. Click inside and select all text
+3. Type: 0 (zero)
+4. Press Tab or click outside the field
+5. Observe what happens to the value and any validation messages</t>
+  </si>
+  <si>
+    <t>1. One of these should happen:
+   a. The value automatically changes to 1 (minimum allowed), OR
+   b. A validation error/warning appears, OR
+   c. The field doesn't accept 0
+2. You cannot run 0 replications - at least 1 is required
+3. Document the actual behavior you observe
+4. This tests the minimum value constraint</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Basic Settings tab
+3. Expand the 'Advanced Settings' section
+4. The model is currently in 'Clock' time mode</t>
+  </si>
+  <si>
+    <t>1. Find the 'Time Mode' dropdown in Advanced Settings
+   - It should currently show 'Clock' or similar
+2. Click on the dropdown to open it
+3. Select 'CalendarDate' or 'Calendar Date' from the options
+4. Observe the changes to the form</t>
+  </si>
+  <si>
+    <t>1. The Time Mode dropdown now shows 'CalendarDate'
+2. The form should change significantly:
+   - Run Time numeric field DISAPPEARS
+   - Run Time unit dropdown DISAPPEARS
+   - Date fields APPEAR: Start Date, Finish Date
+   - Warmup Date field may appear (instead of Warmup Time)
+3. The Save button should become enabled
+4. Calendar mode uses real dates instead of time units</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Basic Settings tab
+3. Expand the 'Advanced Settings' section
+4. The model is currently in 'CalendarDate' time mode</t>
+  </si>
+  <si>
+    <t>1. Find the 'Time Mode' dropdown in Advanced Settings
+   - It should currently show 'CalendarDate'
+2. Click on the dropdown to open it
+3. Select 'Clock' from the options
+4. Observe the changes to the form</t>
+  </si>
+  <si>
+    <t>1. The Time Mode dropdown now shows 'Clock'
+2. The form should change significantly:
+   - Date fields DISAPPEAR (Start Date, Finish Date)
+   - Run Time numeric field APPEARS
+   - Run Time unit dropdown APPEARS
+   - Warmup Time field appears (instead of Warmup Date)
+3. The Save button should become enabled
+4. Clock mode uses time units instead of real dates</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Basic Settings tab
+3. Expand the 'Advanced Settings' section
+4. The model is in 'Clock' time mode</t>
+  </si>
+  <si>
+    <t>1. Find the 'Clock Unit' dropdown in Advanced Settings
+   - This is different from the Run Time unit
+   - Clock Unit is the base time unit for the entire simulation
+2. Click on the dropdown to open it
+3. Select 'Minutes' from the options
+4. Observe the change</t>
+  </si>
+  <si>
+    <t>1. The Clock Unit dropdown now shows 'Minutes'
+2. The Save button should become enabled
+3. This sets the base time unit for all calculations in the simulation
+4. All time values will be interpreted in minutes
+5. Click Save to persist the change</t>
+  </si>
+  <si>
+    <t>1. Find the 'Warmup Time' numeric field in Advanced Settings
+   - Warmup is the initial period where statistics aren't collected
+2. Click inside the field
+3. Select all existing text (may be 0 or empty)
+4. Type: 10
+5. Press Tab or click outside the field</t>
+  </si>
+  <si>
+    <t>1. The Warmup Time field now shows 10
+2. The Save button should become enabled
+3. This sets a 10 time-unit warmup period
+4. During warmup, the simulation runs but doesn't collect statistics
+5. Warmup helps the model reach a 'steady state' before measuring
+6. Click Save to persist the change</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Basic Settings tab
+3. The model must be in 'CalendarDate' time mode
+   (Check Advanced Settings &gt; Time Mode if needed)</t>
+  </si>
+  <si>
+    <t>1. Find the 'Start Date' field in the Basic Settings panel
+   - This should be visible when in Calendar Date mode
+   - May show a date picker icon or be a text field
+2. Click on the field or the date picker icon
+3. A date/time picker should appear
+4. Select a date: January 15, 2024 (or any date)
+5. Optionally set a time (e.g., 8:00 AM)
+6. Confirm or close the picker</t>
+  </si>
+  <si>
+    <t>1. The Start Date field now shows your selected date
+   - Example: '2024-01-15' or '01/15/2024 8:00 AM'
+2. The Save button should become enabled
+3. This sets when the simulation begins
+4. All simulation events will start from this date/time
+5. Click Save to persist the change</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Basic Settings tab
+3. The model is in 'CalendarDate' time mode
+4. A Start Date has been set</t>
+  </si>
+  <si>
+    <t>1. Find the 'Finish Date' field in the Basic Settings panel
+   - Should be below or near the Start Date field
+2. Click on the field or the date picker icon
+3. A date/time picker should appear
+4. Select a date AFTER the start date: January 31, 2024
+5. Optionally set a time (e.g., 5:00 PM)
+6. Confirm or close the picker</t>
+  </si>
+  <si>
+    <t>1. The Finish Date field now shows your selected date
+   - Example: '2024-01-31' or '01/31/2024 5:00 PM'
+2. The Save button should become enabled
+3. The finish date must be AFTER the start date
+4. The simulation will run from Start Date to Finish Date
+5. Click Save to persist the change</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Basic Settings tab
+3. The model is in 'CalendarDate' time mode
+4. Expand Advanced Settings if the warmup field is there</t>
+  </si>
+  <si>
+    <t>1. Find the 'Warmup Date' or 'Warmup End Date' field
+   - May be in Basic Settings or Advanced Settings
+   - This defines when the warmup period ends
+2. Click on the field or the date picker icon
+3. Select a date AFTER the start date but BEFORE the finish date
+   - Example: If start is Jan 15, pick Jan 17
+4. Confirm the selection</t>
+  </si>
+  <si>
+    <t>1. The Warmup Date field shows your selected date
+2. The Save button should become enabled
+3. The warmup date must be:
+   - AFTER the Start Date
+   - BEFORE the Finish Date
+4. Statistics will only be collected AFTER the warmup date
+5. This allows the model to 'warm up' before measuring</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Basic Settings tab
+3. The model is in 'CalendarDate' time mode
+4. A Start Date is currently set</t>
+  </si>
+  <si>
+    <t>1. Find the Start Date field that has a value
+2. Look for a way to clear the date:
+   - A clear button (X) next to the field
+   - Or select all text and press Delete
+   - Or click a 'Clear' option in the date picker
+3. Clear the date value
+4. Observe the field and any validation messages</t>
+  </si>
+  <si>
+    <t>1. The Start Date field should now be empty or show placeholder text
+2. The Save button may become enabled
+3. A validation warning/error may appear:
+   - 'Start date is required' or similar
+4. In Calendar mode, start date is typically required
+5. Document the actual behavior you observe</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Basic Settings tab
+3. The model is in 'CalendarDate' time mode
+4. A Start Date is set (e.g., January 15, 2024)</t>
+  </si>
+  <si>
+    <t>1. Note the current Start Date (e.g., January 15, 2024)
+2. Find the Finish Date field
+3. Set the Finish Date to a date BEFORE the Start Date:
+   - If Start is Jan 15, set Finish to Jan 10
+4. Confirm the date selection
+5. Look for validation messages in the panel or when trying to save</t>
+  </si>
+  <si>
+    <t>1. A validation error or warning should appear
+2. The message should indicate the date conflict:
+   - 'Finish date must be after start date'
+   - Or 'Invalid date range'
+3. The Save button may be disabled OR
+4. Saving may be blocked with an error message
+5. This is correct validation behavior - dates must be in order</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Basic Settings tab
+3. The model is in 'CalendarDate' time mode
+4. Start Date is set (e.g., Jan 15) and Finish Date is set (e.g., Jan 31)</t>
+  </si>
+  <si>
+    <t>1. Find the Warmup Date field
+2. Try setting the Warmup Date to BEFORE the Start Date:
+   - If Start is Jan 15, set Warmup to Jan 10
+3. Confirm the date selection
+4. Look for validation messages
+5. Also try setting Warmup AFTER the Finish Date to test both boundaries</t>
+  </si>
+  <si>
+    <t>1. A validation error or warning should appear
+2. The message should indicate:
+   - 'Warmup date must be after start date', OR
+   - 'Warmup date must be before finish date'
+3. Warmup must be within the simulation date range
+4. Document the actual validation behavior
+5. Both boundaries should be enforced</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Basic Settings tab
+3. The model is in 'CalendarDate' time mode
+4. Date fields are visible (Start Date, Finish Date, Warmup Date)</t>
+  </si>
+  <si>
+    <t>1. Look for info icons (usually a circled 'i' or '?') next to date fields
+2. Hover your mouse over the info icon next to Start Date
+3. Hold still for 1-2 seconds and read any tooltip
+4. Repeat for Finish Date info icon
+5. Repeat for Warmup Date info icon (if present)</t>
+  </si>
+  <si>
+    <t>1. Each date field should have a tooltip explaining its purpose:
+   - Start Date: When the simulation begins
+   - Finish Date: When the simulation ends
+   - Warmup Date: When to start collecting statistics
+2. Tooltips appear after hovering for 1-2 seconds
+3. Tooltips help users understand what each field controls
+4. Document the tooltip text you observe</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel
+3. Click the States tab (second tab from left)</t>
+  </si>
+  <si>
+    <t>1. Look for an 'Add State' button or '+' icon in the States panel
+   - This is usually at the top or bottom of the states list
+2. Click the 'Add State' or '+' button
+3. Observe what happens in the states list below
+4. A new state should appear in the list</t>
+  </si>
+  <si>
+    <t>1. A new state is added to the list immediately
+2. The new state may have a default name like 'New State' or 'State 1'
+3. The state name field may be editable immediately (cursor in text box)
+4. IMPORTANT: Changes save automatically - no Save button needed on this tab
+5. The states list now shows one more item than before
+6. These are MODEL-level states (different from Entity states)</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; States tab
+3. At least one state exists in the list</t>
+  </si>
+  <si>
+    <t>1. Find a state in the list (e.g., 'New State' or any existing state)
+2. Click on the state name to select it for editing
+   - Or click an edit icon/pencil if present
+3. The name should become editable (text box with cursor)
+4. Delete the existing name and type a new name: 'Running'
+5. Press Enter or click outside the text box</t>
+  </si>
+  <si>
+    <t>1. The state name changes to 'Running' immediately
+2. The change is saved automatically (no Save button to click)
+3. The state remains in the list with its new name
+4. No error messages appear
+5. If you navigate away and come back, the name 'Running' persists</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; States tab
+3. At least one state exists in the list that you can delete</t>
+  </si>
+  <si>
+    <t>1. Find a state you want to delete in the list
+2. Look for a delete button next to the state:
+   - May be a trash can icon
+   - May be an 'X' button
+   - May appear when you hover over the state row
+3. Click the delete button for that state
+4. If a confirmation dialog appears, confirm the deletion</t>
+  </si>
+  <si>
+    <t>1. The state is removed from the list immediately
+2. The deletion is saved automatically (no Save button needed)
+3. The states list now shows one fewer item
+4. If you navigate away and come back, the deleted state is still gone
+5. No error messages appear during deletion
+6. Note: Deleting a state in use by entities may show a warning</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; States tab</t>
+  </si>
+  <si>
+    <t>1. Add a new state by clicking the 'Add State' or '+' button
+2. Type a name for the state: 'Maintenance Mode'
+3. Press Enter or click outside the text box
+4. DO NOT look for or click a Save button
+5. Click on a different tab (e.g., Basic Settings tab)
+6. Click back to the States tab
+7. Check if your state is still there</t>
+  </si>
+  <si>
+    <t>1. When you return to the States tab, the 'Maintenance Mode' state should still be there
+2. This proves that states save automatically without clicking Save
+3. There is no Save button visible on the States tab
+4. All changes (add, edit, delete) are saved immediately
+5. This is different from Basic Settings, which requires manual save
+6. Auto-save provides a smoother editing experience for list-based data</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel
+3. Click the Requirements tab (third tab from left)</t>
+  </si>
+  <si>
+    <t>1. Look for an 'Add' or '+' button in the Resource Requirements panel
+   - Usually at the top of the requirements list
+2. Click the 'Add' button
+3. Observe what happens - a modal dialog should open</t>
+  </si>
+  <si>
+    <t>1. A modal dialog opens for creating a new requirement
+2. The modal should have fields for:
+   - Requirement name
+   - Resource selection (which resources are needed)
+   - Quantity or configuration options
+3. The modal has Save/Cancel buttons
+4. This is where you define resource needs for activities</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Requirements tab
+3. Click 'Add' to open the requirement modal
+4. The modal is open and empty</t>
+  </si>
+  <si>
+    <t>1. In the requirement modal, find the 'Name' field
+2. Type a name: 'Operator Required'
+3. Configure the resources needed:
+   - Select which resource(s) this requirement uses
+   - Set quantities if applicable
+4. Click the 'Save' button in the modal
+5. Observe the requirements list</t>
+  </si>
+  <si>
+    <t>1. The modal closes after clicking Save
+2. A new requirement 'Operator Required' appears in the list
+3. The requirement shows the configured resources
+4. Changes are saved automatically (no main Save button needed)
+5. The requirement is now available to assign to activities</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Requirements tab
+3. At least one requirement exists in the list</t>
+  </si>
+  <si>
+    <t>1. Find a requirement in the list
+2. Look for an 'Edit' button or pencil icon next to it
+   - Or the requirement row may be clickable
+3. Click to edit the requirement
+4. The modal should open with the existing data populated</t>
+  </si>
+  <si>
+    <t>1. The requirement modal opens
+2. The modal shows the existing requirement data:
+   - Name field has current name
+   - Resource selections are pre-filled
+3. You can modify any field
+4. Click Save to apply changes or Cancel to discard
+5. This allows updating requirement configurations</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Requirements tab
+3. A requirement exists that is NOT being used by any activity</t>
+  </si>
+  <si>
+    <t>1. Find a requirement you want to delete
+2. Look for a 'Delete' button or trash icon next to it
+3. Click the delete button
+4. If a confirmation appears, confirm the deletion
+5. Observe the requirements list</t>
+  </si>
+  <si>
+    <t>1. The requirement is removed from the list
+2. The deletion saves automatically
+3. The requirements list now shows one fewer item
+4. No error messages appear
+5. Note: This works easily when the requirement is unused</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Requirements tab
+3. A requirement exists that IS being used by one or more activities</t>
+  </si>
+  <si>
+    <t>1. Find a requirement that is assigned to activities
+   - It may show a usage count or indicator
+2. Click the delete button for this requirement
+3. Observe what happens:
+   - Does a warning appear?
+   - Is the deletion blocked?
+4. Note the behavior</t>
+  </si>
+  <si>
+    <t>1. A warning should appear indicating the requirement is in use
+2. The warning may show:
+   - 'This requirement is used by X activities'
+   - List of activities using this requirement
+3. You may be asked to confirm deletion anyway
+4. Or the deletion may be blocked until usages are removed
+5. This prevents accidental deletion of active requirements</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Requirements tab
+3. Click 'Add' to open a new requirement modal
+4. The modal is open</t>
+  </si>
+  <si>
+    <t>1. In the modal, type a name: 'Test Requirement'
+2. Configure some resource settings
+3. DO NOT click Save
+4. Click the 'Cancel' button or 'X' to close the modal
+5. Observe the requirements list</t>
+  </si>
+  <si>
+    <t>1. The modal closes without saving
+2. The requirements list does NOT show 'Test Requirement'
+3. No new requirement was created
+4. Your changes were discarded
+5. This is the expected cancel behavior</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Requirements tab</t>
+  </si>
+  <si>
+    <t>1. Add a new requirement via the modal and save it
+2. Note there is no main 'Save' button at the bottom of the Requirements tab
+3. Click to a different tab (e.g., Basic Settings)
+4. Click back to the Requirements tab
+5. Check if your requirement is still there</t>
+  </si>
+  <si>
+    <t>1. Your saved requirement persists after switching tabs
+2. Requirements save automatically when you save the modal
+3. There is no main Save/Cancel button on the Requirements tab
+4. Each modal save immediately persists the change
+5. This is consistent with other auto-save tabs (States, Scenarios)</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. The model has Resource shapes in the diagram
+3. Open the Model Panel &gt; Requirements tab</t>
+  </si>
+  <si>
+    <t>1. Look at the requirements list
+2. Check if there are requirements you didn't manually create
+3. These may be labeled as 'auto-generated' or have a special indicator
+4. Compare the list to your Resource shapes in the diagram</t>
+  </si>
+  <si>
+    <t>1. Auto-generated requirements may appear in the list
+2. These are created automatically based on Resource shapes
+3. They may have names matching your Resource names
+4. Auto-generated requirements help simplify initial setup
+5. You can edit them if needed to customize the configuration</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Requirements tab
+3. An auto-generated requirement exists in the list</t>
+  </si>
+  <si>
+    <t>1. Find an auto-generated requirement
+2. Click to edit it (Edit button or click the row)
+3. The modal should open with the auto-generated configuration
+4. Make a change (e.g., modify the name or quantity)
+5. Click Save</t>
+  </si>
+  <si>
+    <t>1. The modal opens showing the auto-generated requirement data
+2. You can modify the fields just like manual requirements
+3. After saving, your changes are preserved
+4. The requirement may lose its 'auto-generated' indicator
+5. You have full control to customize as needed</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. The model has NO Resource shapes in the diagram
+3. No requirements have been manually created</t>
+  </si>
+  <si>
+    <t>1. Open the Model Panel
+2. Click the Requirements tab
+3. Observe the requirements list area
+4. Note any messages or empty state indicators</t>
+  </si>
+  <si>
+    <t>1. The requirements list should be empty OR
+2. A message may appear like:
+   - 'No requirements defined'
+   - 'Add resources to your model to create requirements'
+3. The 'Add' button should still be visible and functional
+4. This is the expected state for a model without resources
+5. Add Resource shapes or manually create requirements to populate</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel</t>
+  </si>
+  <si>
+    <t>1. Look at the tab icons at the top of the Model Panel
+2. Find the Scenarios tab (fourth tab from left)
+3. Click on the Scenarios tab icon
+4. Observe the panel content that appears</t>
+  </si>
+  <si>
+    <t>1. The Scenarios panel displays correctly
+2. You should see:
+   - A list of scenarios (may be empty or have a default scenario)
+   - Options to create new scenarios
+   - Edit/delete buttons for existing scenarios
+3. Scenarios allow running different 'what-if' simulations
+4. Each scenario can have different parameter values</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Scenarios tab</t>
+  </si>
+  <si>
+    <t>1. Look for a 'Create Scenario', 'Add', or '+' button
+2. Click the button to create a new scenario
+3. A form or modal may appear for scenario configuration
+4. Enter a name for the scenario: 'High Volume Test'
+5. Configure any scenario-specific parameters if prompted
+6. Save or confirm the creation</t>
+  </si>
+  <si>
+    <t>1. A new scenario 'High Volume Test' appears in the list
+2. The scenario may show:
+   - Name
+   - Status (e.g., 'Not run', 'Draft')
+   - Configuration summary
+3. Changes are saved automatically
+4. You can now select this scenario for simulation runs
+5. The scenarios list shows one more item</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Scenarios tab
+3. At least one scenario exists in the list</t>
+  </si>
+  <si>
+    <t>1. Find a scenario in the list
+2. Click to edit or select the scenario:
+   - May be an Edit button/icon
+   - Or click on the scenario row
+3. Modify scenario parameters:
+   - Change the name
+   - Adjust any configurable values
+4. Save the changes</t>
+  </si>
+  <si>
+    <t>1. The scenario editor or form opens
+2. You can modify:
+   - Scenario name
+   - Any scenario-specific parameters
+3. After saving, changes are visible in the list
+4. Changes persist when switching tabs
+5. The scenario is ready to run with new settings</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Scenarios tab
+3. At least one scenario exists (not the only/default scenario)</t>
+  </si>
+  <si>
+    <t>1. Find a scenario you want to delete
+2. Look for a 'Delete' button or trash icon
+3. Click to delete the scenario
+4. If a confirmation dialog appears, confirm the deletion
+5. Observe the scenarios list</t>
+  </si>
+  <si>
+    <t>1. The scenario is removed from the list
+2. The deletion saves automatically
+3. The scenarios list now shows one fewer item
+4. If this was a scenario with results, the results are also removed
+5. Note: You may not be able to delete the last/default scenario</t>
+  </si>
+  <si>
+    <t>1. Create a new scenario or edit an existing one
+2. Note there is no main 'Save' button at the bottom of the Scenarios tab
+3. Click to a different tab (e.g., Basic Settings)
+4. Click back to the Scenarios tab
+5. Check if your scenario changes are still there</t>
+  </si>
+  <si>
+    <t>1. Your scenario changes persist after switching tabs
+2. Scenarios save automatically
+3. There is no main Save/Cancel button on the Scenarios tab
+4. Each action (create, edit, delete) is immediately saved
+5. This is consistent with other auto-save tabs (States, Requirements)</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Scenarios tab
+3. Create multiple scenarios (at least 3)</t>
+  </si>
+  <si>
+    <t>1. Ensure you have multiple scenarios in the list:
+   - 'Default' or 'Baseline'
+   - 'High Volume Test'
+   - 'Low Resource Scenario'
+2. Observe how the list displays multiple scenarios
+3. Check if you can:
+   - See all scenarios clearly
+   - Distinguish between them
+   - Select different scenarios</t>
+  </si>
+  <si>
+    <t>1. All scenarios are listed and visible
+2. Each scenario shows its name and status
+3. You can select different scenarios for editing
+4. The list may be scrollable if many scenarios exist
+5. Multiple scenarios enable comparison of different configurations
+6. Each scenario can be run independently for 'what-if' analysis</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. The model has some issues (errors or warnings)
+3. Open the Model Panel</t>
+  </si>
+  <si>
+    <t>1. Click the Validation tab (fifth tab from left)
+2. Watch for any loading indicator
+3. Observe when validation results appear
+4. Note if validation runs automatically or requires a manual trigger</t>
+  </si>
+  <si>
+    <t>1. Validation should run automatically when you open the tab
+2. You may see a brief loading indicator
+3. Results appear without clicking a 'Validate' button
+4. Errors (red) and warnings (yellow) are displayed
+5. This automatic behavior helps catch issues early</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. The model has validation ERRORS (not just warnings)
+   - Example: Missing required elements</t>
+  </si>
+  <si>
+    <t>1. Open the Model Panel &gt; Validation tab
+2. Look for items marked as ERRORS
+   - Usually displayed in RED
+   - May have an error icon (X or !)
+3. Read the error messages
+4. Note how many errors are shown</t>
+  </si>
+  <si>
+    <t>1. Errors are displayed in the validation dashboard
+2. Errors appear in RED or with error styling
+3. Each error shows:
+   - Error message describing the problem
+   - Element name or type affected
+4. Errors typically block simulation from running
+5. All errors should be fixed before simulating</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. The model has validation WARNINGS
+   - Example: Using default names, unused elements</t>
+  </si>
+  <si>
+    <t>1. Open the Model Panel &gt; Validation tab
+2. Look for items marked as WARNINGS
+   - Usually displayed in YELLOW or ORANGE
+   - May have a warning icon (⚠)
+3. Read the warning messages
+4. Note how many warnings are shown</t>
+  </si>
+  <si>
+    <t>1. Warnings are displayed in the validation dashboard
+2. Warnings appear in YELLOW/ORANGE or with warning styling
+3. Each warning shows:
+   - Warning message describing the concern
+   - Element name or type affected
+4. Warnings don't block simulation, but indicate potential issues
+5. Consider addressing warnings for best results</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. The model is complete and valid:
+   - Has generators, activities, entities
+   - All required fields are filled
+   - No configuration errors</t>
+  </si>
+  <si>
+    <t>1. Open the Model Panel &gt; Validation tab
+2. Observe the validation dashboard
+3. Look for any errors or warnings
+4. Check for a success message or indicator</t>
+  </si>
+  <si>
+    <t>1. The validation dashboard shows no errors
+2. Either:
+   - An empty error list, OR
+   - A success message like 'Model is valid'
+   - A green checkmark or success indicator
+3. Warnings may still appear (they're informational)
+4. The model is ready to run simulation
+5. This is the goal state for a complete model</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. The model has at least one validation error or warning
+3. Open the Model Panel &gt; Validation tab</t>
+  </si>
+  <si>
+    <t>1. Find an error or warning in the validation list
+2. Click directly on the error/warning item
+3. Observe what happens:
+   - Does the view change?
+   - Is an element selected/highlighted?
+   - Does an editor open?</t>
+  </si>
+  <si>
+    <t>1. Clicking should navigate to the problem element:
+   - The diagram may zoom/pan to show the element
+   - The element may become selected (highlighted border)
+   - The element's editor panel may open
+2. This helps you quickly find and fix issues
+3. You can now edit the element to resolve the validation issue
+4. Document actual navigation behavior</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. The model has validation errors
+3. Open the Model Panel</t>
+  </si>
+  <si>
+    <t>1. Look at the Validation tab icon (fifth tab)
+2. Before clicking it, observe if there's a badge or indicator
+3. The badge may show a number (error count)
+4. Note the badge color and number</t>
+  </si>
+  <si>
+    <t>1. The Validation tab icon should show a badge with error count
+2. Badge typically shows:
+   - A number (e.g., '3' for 3 errors)
+   - Red or warning color
+3. This provides quick visibility of issues without opening the tab
+4. The count updates as you fix or create errors
+5. When all errors are fixed, the badge may disappear</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. The model has a validation error
+3. The Validation tab is open showing the error</t>
+  </si>
+  <si>
+    <t>1. Note the current validation error
+2. Go fix the error:
+   - Click on the problematic element
+   - Make the necessary correction
+   - Save if required
+3. Return to the Validation tab
+4. Observe if the validation results update</t>
+  </si>
+  <si>
+    <t>1. After fixing the issue, validation should refresh
+2. The error you fixed should no longer appear
+3. This may happen:
+   - Automatically when you return to the tab
+   - After a brief delay
+   - When clicking a refresh button (if present)
+4. The error count should decrease
+5. This confirms your fix was successful</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Create or have a Generator shape with NO outgoing connectors
+   - The generator is not connected to any activity</t>
+  </si>
+  <si>
+    <t>1. Ensure you have a generator that isn't connected to anything
+2. Open the Model Panel &gt; Validation tab
+3. Look for an error related to this generator
+4. Read the error message</t>
+  </si>
+  <si>
+    <t>1. An ERROR should appear for the disconnected generator
+2. The error message should indicate:
+   - 'Generator has no outgoing connectors'
+   - 'Entities cannot flow into the system'
+   - Or similar wording about missing connections
+3. This is a critical error - entities need somewhere to go
+4. Fix by connecting the generator to an activity</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Create a generator that connects to activities in a loop
+   - Generator → Activity A → Activity B → Activity A (loop)
+   - NO activity is marked as terminal (exit point)</t>
+  </si>
+  <si>
+    <t>1. Create the loop scenario described in preconditions
+2. Ensure no activity in the path is terminal
+3. Open the Model Panel &gt; Validation tab
+4. Look for path-related errors</t>
+  </si>
+  <si>
+    <t>1. An ERROR should appear about the path
+2. The error message should indicate:
+   - 'Generator has no path to a terminal Activity'
+   - 'All paths lead to dead-ends or loops without exits'
+3. Entities would be stuck in infinite loop
+4. Fix by marking one activity as terminal (exit point)</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Create: Generator → Activity A → Activity B
+3. Activity B has NO outgoing connector and is NOT terminal</t>
+  </si>
+  <si>
+    <t>1. Create the dead-end scenario described
+2. Activity B is a dead-end (no exit, not terminal)
+3. Open the Model Panel &gt; Validation tab
+4. Look for path-related errors</t>
+  </si>
+  <si>
+    <t>1. An ERROR should appear about the dead-end path
+2. The error message should indicate:
+   - 'Generator has paths that lead to non-terminal Activities with no exit'
+   - 'Entities may get stuck'
+3. Entities would reach Activity B and have nowhere to go
+4. Fix by either:
+   - Adding an outgoing connector from Activity B
+   - Marking Activity B as terminal</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Create a complete valid flow:
+   - Generator → Activity A → Activity B (terminal)</t>
+  </si>
+  <si>
+    <t>1. Create the valid path scenario
+2. Ensure Activity B is marked as terminal (exit point)
+3. Open the Model Panel &gt; Validation tab
+4. Check for any path validation errors</t>
+  </si>
+  <si>
+    <t>1. NO path validation errors should appear for this generator
+2. The flow is valid because:
+   - Generator connects to an activity
+   - There's a path to a terminal activity
+   - Entities have a way to exit the system
+3. Other errors/warnings may exist for different issues
+4. This is the correct flow structure</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Create a loop WITH a valid exit:
+   - Generator → A → B → A (loop)
+   - A also connects to C (terminal)</t>
+  </si>
+  <si>
+    <t>1. Create the loop-with-exit scenario
+2. The key: Activity A has two paths:
+   - One path loops back (A → B → A)
+   - One path exits to terminal (A → C terminal)
+3. Open the Model Panel &gt; Validation tab
+4. Check for path validation errors</t>
+  </si>
+  <si>
+    <t>1. NO path validation errors should appear
+2. The loop is acceptable because:
+   - There IS a path to terminal activity C
+   - Entities aren't guaranteed to loop forever
+   - They can eventually exit through A → C
+3. Loops are valid as long as exit path exists
+4. This is a common pattern for retry/rework flows</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Create two generators:
+   - Generator 1: Has path issues (no terminal)
+   - Generator 2: Has path issues (disconnected)</t>
+  </si>
+  <si>
+    <t>1. Set up both generators with different path problems
+2. Open the Model Panel &gt; Validation tab
+3. Look at all the validation errors
+4. Check if errors are shown for BOTH generators</t>
+  </si>
+  <si>
+    <t>1. Errors should appear for BOTH generators
+2. Each generator's issues are validated independently
+3. You should see:
+   - Error for Generator 1 (no terminal path)
+   - Error for Generator 2 (no outgoing connectors)
+4. Both need to be fixed before simulation
+5. Each error identifies which generator has the problem</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. The model has NO generator shapes
+   - Delete all generators or start fresh</t>
+  </si>
+  <si>
+    <t>1. Ensure the model has zero generators
+2. Open the Model Panel &gt; Validation tab
+3. Look for model-level errors
+4. Check for a 'no generators' error</t>
+  </si>
+  <si>
+    <t>1. An ERROR should appear about missing generators
+2. The error message should indicate:
+   - 'Model must have at least one generator'
+   - 'No generators defined'
+3. Generators are required - they create entities
+4. Without generators, nothing enters the simulation
+5. Add at least one Generator shape to fix</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. The model has a generator but NO activity shapes
+   - Delete all activities or have only generator</t>
+  </si>
+  <si>
+    <t>1. Ensure the model has zero activities (but has a generator)
+2. Open the Model Panel &gt; Validation tab
+3. Look for model-level errors
+4. Check for a 'no activities' error</t>
+  </si>
+  <si>
+    <t>1. An ERROR should appear about missing activities
+2. The error message should indicate:
+   - 'Model must have at least one activity'
+   - 'No activities defined'
+3. Activities are required - they process entities
+4. Entities need activities to flow through
+5. Add at least one Activity shape to fix</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. The model has NO entity shapes
+   - Delete all entities</t>
+  </si>
+  <si>
+    <t>1. Ensure the model has zero entities
+2. Open the Model Panel &gt; Validation tab
+3. Look for model-level errors
+4. Check for a 'no entities' error</t>
+  </si>
+  <si>
+    <t>1. An ERROR should appear about missing entities
+2. The error message should indicate:
+   - 'Model must have at least one entity'
+   - 'No entities defined'
+3. Entities are required - they represent what flows through
+4. Without entities, generators have nothing to create
+5. Add at least one Entity shape to fix</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. The model has:
+   - At least one Generator
+   - At least one Activity
+   - At least one Entity
+3. Elements are properly connected</t>
+  </si>
+  <si>
+    <t>1. Verify you have all three required element types
+2. Open the Model Panel &gt; Validation tab
+3. Check for element count errors
+4. Specifically look for 'no generators/activities/entities' errors</t>
+  </si>
+  <si>
+    <t>1. NO element count errors should appear
+2. The model meets minimum requirements:
+   - Has generator(s) ✓
+   - Has activity(s) ✓
+   - Has entity(s) ✓
+3. Other errors may still exist (path issues, configuration)
+4. But the basic element requirements are satisfied
+5. This is the foundation for a valid model</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel
+3. Click the Utilities tab (sixth/last tab)</t>
+  </si>
+  <si>
+    <t>1. Look at the Utilities panel content
+2. Find the 'Diagnostics' section
+3. Look for a 'View Model JSON' button
+4. Note the button's location and appearance</t>
+  </si>
+  <si>
+    <t>1. A 'View Model JSON' button should be visible
+2. The button is typically in a 'Diagnostics' section
+3. The button should be clickable (not disabled)
+4. This tool is for debugging and advanced users
+5. It shows the internal model data structure</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Utilities tab
+3. The 'View Model JSON' button is visible</t>
+  </si>
+  <si>
+    <t>1. Click the 'View Model JSON' button
+2. Observe what happens:
+   - Does a modal/dialog open?
+   - Does content appear inline?
+3. Look at the content that appears</t>
+  </si>
+  <si>
+    <t>1. A modal or viewer opens showing the model JSON
+2. The JSON content should display:
+   - Formatted/indented JSON structure
+   - Model configuration data
+   - Element definitions (generators, activities, etc.)
+3. The content may be read-only
+4. This is useful for debugging or technical support</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Utilities tab
+3. Click 'View Model JSON'
+4. The JSON viewer modal is open</t>
+  </si>
+  <si>
+    <t>1. Look for a way to close the JSON viewer:
+   - A 'Close' button
+   - An 'X' button in the corner
+   - Click outside the modal (if it's a modal)
+   - Press Escape key
+2. Close the viewer
+3. Observe the return to normal state</t>
+  </si>
+  <si>
+    <t>1. The JSON viewer closes
+2. You return to the Utilities tab view
+3. The 'View Model JSON' button is still available
+4. No errors occur when closing
+5. You can click the button again to reopen</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Utilities tab
+3. Click 'View Model JSON'
+4. The JSON viewer is showing content</t>
+  </si>
+  <si>
+    <t>1. Examine the JSON content displayed
+2. Check if it appears to be valid JSON:
+   - Proper brackets and braces { } [ ]
+   - Quoted string keys
+   - No syntax error indicators
+3. Look for recognizable model data:
+   - Model name
+   - Element IDs
+   - Configuration values</t>
+  </si>
+  <si>
+    <t>1. The JSON should be well-formed and valid
+2. Content should include:
+   - Model configuration (name, run time, etc.)
+   - Elements (generators, activities, entities)
+   - Connections/relationships
+3. The formatting should be readable (indented)
+4. No error messages about invalid JSON
+5. This represents the internal model state</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. You have NOT made any changes to the model yet</t>
+  </si>
+  <si>
+    <t>1. Open the Model Panel
+2. Click the Basic Settings tab (gear icon, first tab)
+3. Look at the bottom of the panel for the Save button
+4. Observe the state of the Save button WITHOUT making any changes</t>
+  </si>
+  <si>
+    <t>1. The Save button should be visible at the bottom right of the panel
+2. The Save button should be DISABLED (grayed out, not clickable)
+3. This is because no changes have been made yet
+4. The Cancel button may or may not be visible
+5. Hovering over the disabled Save button shows it's not clickable</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Basic Settings tab
+3. The Save button is currently disabled (grayed out)</t>
+  </si>
+  <si>
+    <t>1. Find the 'Model Name' text box near the top
+2. Click inside the text box
+3. Make any small change to the name:
+   - Add a letter at the end
+   - Or delete one character
+   - Or change any character
+4. Press Tab or click outside the text box
+5. Look at the Save button at the bottom</t>
+  </si>
+  <si>
+    <t>1. The Save button should now be ENABLED (blue, clickable)
+2. The button text should say 'Save' clearly
+3. The Cancel button should also appear next to it
+4. This indicates you have unsaved changes
+5. The button should respond to hover (cursor changes)</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Basic Settings tab
+3. Make a change to the model name
+4. The Save button is now enabled (blue)</t>
+  </si>
+  <si>
+    <t>1. Note the new name you typed (e.g., 'Test Model Save')
+2. Click the Save button at the bottom right
+3. Watch for any visual feedback (loading indicator, button change)
+4. After save completes, click on a different element in the diagram
+5. Re-open the Model Panel
+6. Check the model name</t>
+  </si>
+  <si>
+    <t>1. When you click Save, the button may briefly show 'Saving...'
+2. After save, the Save button becomes disabled again (grayed out)
+3. The Cancel button may disappear
+4. When you re-open the Model Panel, your saved name 'Test Model Save' is displayed
+5. The change persisted successfully</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Basic Settings tab
+3. Note the ORIGINAL model name (e.g., 'My Simulation')</t>
+  </si>
+  <si>
+    <t>1. Find the 'Model Name' text box
+2. Change the name to something different (e.g., 'SHOULD BE DISCARDED')
+3. The Save button is now enabled
+4. DO NOT click Save
+5. Instead, click the Cancel button (next to Save)
+6. Observe what happens to the model name</t>
+  </si>
+  <si>
+    <t>1. When you click Cancel, the name reverts to the ORIGINAL value ('My Simulation')
+2. The text box now shows the original name, not 'SHOULD BE DISCARDED'
+3. The Save button becomes disabled again (no pending changes)
+4. The Cancel button may disappear
+5. Your changes were discarded without being saved</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Basic Settings tab</t>
+  </si>
+  <si>
+    <t>1. Change the model name to something new (e.g., 'Pending Changes')
+2. The Save button should become enabled
+3. Now click on the States tab (second tab)
+4. Look around the States tab, don't make changes
+5. Click back to the Basic Settings tab (gear icon)
+6. Check the model name and Save button state</t>
+  </si>
+  <si>
+    <t>1. When you return to Basic Settings, your change is still there
+2. The name still shows 'Pending Changes' (not lost)
+3. The Save button is still enabled (change still pending)
+4. Switching tabs does NOT discard your unsaved changes
+5. You can still click Save or Cancel after switching tabs</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Basic Settings tab
+3. Make a change to enable the Save button</t>
+  </si>
+  <si>
+    <t>1. With the Save button enabled (blue), prepare to watch it closely
+2. Click the Save button
+3. Watch the button text and appearance during the save operation
+4. Note any changes in the button while saving</t>
+  </si>
+  <si>
+    <t>1. When clicked, the Save button should show a loading state:
+   - The text may change to 'Saving...' or show a spinner
+   - The button may become temporarily disabled during save
+2. After save completes (usually very quick):
+   - The button returns to normal 'Save' text
+   - The button becomes disabled (grayed out)
+3. This feedback confirms your save is being processed</t>
+  </si>
+  <si>
+    <t>1. Click through the tabs and note Save/Cancel button visibility:
+   - Basic Settings tab (gear icon) - observe footer
+   - States tab - observe footer
+   - Requirements tab - observe footer
+   - Scenarios tab - observe footer
+2. Compare which tabs show Save/Cancel and which don't</t>
+  </si>
+  <si>
+    <t>1. Basic Settings tab: Save/Cancel buttons ARE visible (when changes exist)
+2. States tab: NO Save/Cancel buttons (auto-save)
+3. Requirements tab: NO Save/Cancel buttons (auto-save via modal)
+4. Scenarios tab: NO Save/Cancel buttons (auto-save)
+5. Auto-save tabs don't need manual save buttons
+6. Only Basic Settings requires explicit save</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. The model has been configured (name, run time, etc.)
+3. You are not currently in the Model Panel</t>
+  </si>
+  <si>
+    <t>1. Open the Model Panel
+   - This may be via a menu option or toolbar button
+   - Or by clicking somewhere that opens the Model Panel
+2. The panel should load
+3. Click on the Basic Settings tab (gear icon)
+4. Observe the data that appears in the form</t>
+  </si>
+  <si>
+    <t>1. The Model Panel loads successfully
+2. The Basic Settings form shows the correct model data:
+   - Model name matches what was saved
+   - Run time value is correct
+   - Time mode (Clock or Calendar) is correct
+3. All fields populate with the saved values
+4. No loading errors appear
+5. The data accurately reflects the model configuration</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Basic Settings tab
+3. Make changes but do NOT save (Save button is enabled)</t>
+  </si>
+  <si>
+    <t>1. Change the model name to 'UNSAVED CHANGE'
+2. The Save button should become enabled (blue)
+3. DO NOT click Save - leave the change unsaved
+4. Now click on an element in the diagram (e.g., an Activity)
+   - This should switch focus to the Activity Editor
+5. Re-open the Model Panel
+6. Check the model name in Basic Settings</t>
+  </si>
+  <si>
+    <t>1. When you switch to another element, the Model Panel may close or switch
+2. When you return to the Model Panel:
+   - The unsaved changes may be DISCARDED
+   - The model name shows the ORIGINAL value (not 'UNSAVED CHANGE')
+3. Or alternatively:
+   - A warning may appear about unsaved changes
+4. Document the actual behavior
+5. This tests how unsaved changes are handled on focus change</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Be in a collaborative editing session (multiple users editing same document)
+3. You have the Model Panel open</t>
+  </si>
+  <si>
+    <t>1. Have another user (or another browser window) edit the model:
+   - Change the model name
+   - Save the change
+2. Observe your Model Panel:
+   - Does it automatically update?
+   - Or do you need to close and reopen?
+3. Note any sync behavior or notifications</t>
+  </si>
+  <si>
+    <t>1. The panel should eventually reflect the changes made by the other user
+2. This may happen:
+   - Automatically (real-time sync)
+   - After closing and reopening the panel
+   - After switching tabs within the panel
+3. The updated model name from the other user should appear
+4. There should be no data conflicts or errors
+5. Note: Real-time sync behavior may vary - document observed behavior</t>
+  </si>
+  <si>
+    <t>1. This test requires technical setup or a corrupted model
+2. Normal users cannot easily reproduce this scenario
+3. This tests error handling for programmatic issues</t>
+  </si>
+  <si>
+    <t>1. If possible, create a scenario where the model has missing or corrupted data:
+   - A model with a missing internal ID
+   - Or model data that was corrupted somehow
+2. Try to open the Model Panel
+3. Observe the behavior
+4. Note any error messages displayed</t>
+  </si>
+  <si>
+    <t>1. The system should handle the error gracefully
+2. An error message should appear like:
+   - 'Invalid model data'
+   - 'Unable to load model'
+   - Or similar error indication
+3. The application should NOT crash
+4. Other elements should still be accessible
+5. Note: This is a defensive error handling test</t>
+  </si>
+  <si>
+    <t>1. Find the 'Model Name' text box
+2. Click inside and select all existing text
+3. Type or paste a very long name (500+ characters)
+   Example: repeat 'VeryLongModelNameForTesting' many times
+4. Press Tab or click outside the text box
+5. Observe how the text box handles the long name
+6. Try to save the changes</t>
+  </si>
+  <si>
+    <t>1. The text box should accept the long name without crashing
+2. The text may appear truncated in the display or show a scrollbar
+3. The Save button should become enabled
+4. The panel should remain responsive
+5. If saved and re-opened, the full name should be preserved
+6. Document any character limits or warnings</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Basic Settings tab
+3. Expand Advanced Settings</t>
+  </si>
+  <si>
+    <t>1. Find the 'Replications' field in Advanced Settings
+2. Click inside and select all text
+3. Type a very large number: 999999
+4. Press Tab or click outside the field
+5. Observe how the field handles the large number
+6. Look for any validation messages</t>
+  </si>
+  <si>
+    <t>1. The field should either:
+   a. Accept the large number if valid, OR
+   b. Show a validation warning about practical limits, OR
+   c. Cap the number to a maximum allowed value
+2. The panel should not crash or freeze
+3. Consider: 999999 replications would take very long to run
+4. Document the actual behavior observed
+5. Note any maximum limits enforced</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Basic Settings tab
+3. The model is in 'Clock' time mode</t>
+  </si>
+  <si>
+    <t>1. Find the 'Run Time' numeric field
+2. Click inside and select all text
+3. Type: 0 (zero)
+4. Press Tab or click outside the field
+5. Observe what happens to the value
+6. Look for any validation messages</t>
+  </si>
+  <si>
+    <t>1. One of these should happen:
+   a. The value is accepted (0 run time = instant simulation?), OR
+   b. A validation error appears (run time must be &gt; 0), OR
+   c. The value is automatically corrected to a minimum (e.g., 1)
+2. The panel should not crash
+3. Document the actual behavior
+4. Zero run time may not be practical for simulations</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a Quodsi model
+2. Open the Model Panel &gt; Basic Settings tab
+3. Note the current model name for reference</t>
+  </si>
+  <si>
+    <t>1. Make a change to the model name:
+   - Type a new name like 'UNSAVED REFRESH TEST'
+2. DO NOT click Save - leave the change unsaved
+3. The Save button should be enabled (blue)
+4. Press F5 or Ctrl+R to refresh the browser
+5. Wait for LucidChart to fully reload
+6. Open the Model Panel again
+7. Check the model name</t>
+  </si>
+  <si>
+    <t>1. When refreshing, you may see a browser warning about unsaved changes
+2. After refresh, the page reloads completely
+3. When you open the Model Panel, it shows the ORIGINAL name
+4. The unsaved change 'UNSAVED REFRESH TEST' is LOST
+5. This is expected behavior - browser refresh loses unsaved work
+6. No errors or crashes should occur</t>
+  </si>
+  <si>
+    <t>1. Have a LucidChart document open with a NEW Quodsi model
+2. The model should have default values</t>
+  </si>
+  <si>
+    <t>1. Open the Model Panel &gt; Basic Settings tab
+2. Expand Advanced Settings
+3. Find the 'Random Seed' field
+4. Observe the default value in the field
+5. Note: Random seed controls simulation reproducibility</t>
+  </si>
+  <si>
+    <t>1. The default random seed should be visible
+2. Expected default value: 12345 (or similar standard default)
+3. The seed is a number used for random number generation
+4. Same seed = same random sequence = reproducible results
+5. You can change this value for different random sequences
+6. Document the actual default value observed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <b val="1"/>
+      <color/>
     </font>
   </fonts>
   <fills count="2">
@@ -1288,8 +3037,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+      <alignment/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1593,68 +3345,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col bestFit="true" customWidth="true" max="1" min="1" width="13.21875"/>
+    <col bestFit="true" customWidth="true" max="2" min="2" width="6.88671875"/>
+    <col bestFit="true" customWidth="true" max="3" min="3" width="25.6640625"/>
+    <col bestFit="true" customWidth="true" max="4" min="4" width="13.5546875"/>
+    <col bestFit="true" customWidth="true" max="5" min="5" width="21.6640625"/>
+    <col bestFit="true" customWidth="true" max="6" min="6" width="35.21875"/>
+    <col bestFit="true" customWidth="true" max="7" min="7" width="11.5546875"/>
+    <col bestFit="true" customWidth="true" max="8" min="8" width="6"/>
+    <col bestFit="true" customWidth="true" max="9" min="9" width="7.44140625"/>
+    <col bestFit="true" customWidth="true" max="11" min="11" width="10.77734375"/>
+    <col bestFit="true" customWidth="true" max="12" min="12" width="11.88671875"/>
+    <col bestFit="true" customWidth="true" max="13" min="13" width="5.88671875"/>
+    <col bestFit="true" customWidth="true" max="14" min="14" width="7.6640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1662,19 +3414,43 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>404</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>405</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>406</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>407</v>
+      </c>
+      <c r="G2" t="s">
+        <v>358</v>
+      </c>
+      <c r="H2" t="s">
+        <v>358</v>
+      </c>
+      <c r="I2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J2" t="s">
+        <v>358</v>
+      </c>
+      <c r="K2" t="s">
+        <v>358</v>
+      </c>
+      <c r="L2" t="s">
+        <v>358</v>
+      </c>
+      <c r="M2" t="s">
+        <v>358</v>
+      </c>
+      <c r="N2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -1685,16 +3461,40 @@
         <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>408</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>409</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+        <v>410</v>
+      </c>
+      <c r="G3" t="s">
+        <v>358</v>
+      </c>
+      <c r="H3" t="s">
+        <v>358</v>
+      </c>
+      <c r="I3" t="s">
+        <v>358</v>
+      </c>
+      <c r="J3" t="s">
+        <v>358</v>
+      </c>
+      <c r="K3" t="s">
+        <v>358</v>
+      </c>
+      <c r="L3" t="s">
+        <v>358</v>
+      </c>
+      <c r="M3" t="s">
+        <v>358</v>
+      </c>
+      <c r="N3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -1705,16 +3505,40 @@
         <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>408</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>411</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+        <v>412</v>
+      </c>
+      <c r="G4" t="s">
+        <v>358</v>
+      </c>
+      <c r="H4" t="s">
+        <v>358</v>
+      </c>
+      <c r="I4" t="s">
+        <v>358</v>
+      </c>
+      <c r="J4" t="s">
+        <v>358</v>
+      </c>
+      <c r="K4" t="s">
+        <v>358</v>
+      </c>
+      <c r="L4" t="s">
+        <v>358</v>
+      </c>
+      <c r="M4" t="s">
+        <v>358</v>
+      </c>
+      <c r="N4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -1725,16 +3549,40 @@
         <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>408</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>413</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+        <v>414</v>
+      </c>
+      <c r="G5" t="s">
+        <v>358</v>
+      </c>
+      <c r="H5" t="s">
+        <v>358</v>
+      </c>
+      <c r="I5" t="s">
+        <v>358</v>
+      </c>
+      <c r="J5" t="s">
+        <v>358</v>
+      </c>
+      <c r="K5" t="s">
+        <v>358</v>
+      </c>
+      <c r="L5" t="s">
+        <v>358</v>
+      </c>
+      <c r="M5" t="s">
+        <v>358</v>
+      </c>
+      <c r="N5" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -1745,16 +3593,40 @@
         <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>408</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>415</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+        <v>416</v>
+      </c>
+      <c r="G6" t="s">
+        <v>358</v>
+      </c>
+      <c r="H6" t="s">
+        <v>358</v>
+      </c>
+      <c r="I6" t="s">
+        <v>358</v>
+      </c>
+      <c r="J6" t="s">
+        <v>358</v>
+      </c>
+      <c r="K6" t="s">
+        <v>358</v>
+      </c>
+      <c r="L6" t="s">
+        <v>358</v>
+      </c>
+      <c r="M6" t="s">
+        <v>358</v>
+      </c>
+      <c r="N6" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -1765,16 +3637,40 @@
         <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>408</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>417</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+        <v>418</v>
+      </c>
+      <c r="G7" t="s">
+        <v>358</v>
+      </c>
+      <c r="H7" t="s">
+        <v>358</v>
+      </c>
+      <c r="I7" t="s">
+        <v>358</v>
+      </c>
+      <c r="J7" t="s">
+        <v>358</v>
+      </c>
+      <c r="K7" t="s">
+        <v>358</v>
+      </c>
+      <c r="L7" t="s">
+        <v>358</v>
+      </c>
+      <c r="M7" t="s">
+        <v>358</v>
+      </c>
+      <c r="N7" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>41</v>
       </c>
@@ -1785,16 +3681,40 @@
         <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>419</v>
       </c>
       <c r="E8" t="s">
-        <v>43</v>
+        <v>420</v>
       </c>
       <c r="F8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+        <v>421</v>
+      </c>
+      <c r="G8" t="s">
+        <v>358</v>
+      </c>
+      <c r="H8" t="s">
+        <v>358</v>
+      </c>
+      <c r="I8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K8" t="s">
+        <v>358</v>
+      </c>
+      <c r="L8" t="s">
+        <v>358</v>
+      </c>
+      <c r="M8" t="s">
+        <v>358</v>
+      </c>
+      <c r="N8" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -1805,13 +3725,37 @@
         <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>422</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>423</v>
       </c>
       <c r="F9" t="s">
-        <v>48</v>
+        <v>424</v>
+      </c>
+      <c r="G9" t="s">
+        <v>358</v>
+      </c>
+      <c r="H9" t="s">
+        <v>358</v>
+      </c>
+      <c r="I9" t="s">
+        <v>358</v>
+      </c>
+      <c r="J9" t="s">
+        <v>358</v>
+      </c>
+      <c r="K9" t="s">
+        <v>358</v>
+      </c>
+      <c r="L9" t="s">
+        <v>358</v>
+      </c>
+      <c r="M9" t="s">
+        <v>358</v>
+      </c>
+      <c r="N9" t="s">
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -1822,67 +3766,67 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col bestFit="true" customWidth="true" max="1" min="1" width="13.44140625"/>
+    <col bestFit="true" customWidth="true" max="2" min="2" width="6.88671875"/>
+    <col bestFit="true" customWidth="true" max="4" min="3" width="21.5546875"/>
+    <col bestFit="true" customWidth="true" max="5" min="5" width="25.88671875"/>
+    <col bestFit="true" customWidth="true" max="6" min="6" width="28.77734375"/>
+    <col bestFit="true" customWidth="true" max="7" min="7" width="11.5546875"/>
+    <col bestFit="true" customWidth="true" max="8" min="8" width="6"/>
+    <col bestFit="true" customWidth="true" max="9" min="9" width="7.44140625"/>
+    <col bestFit="true" customWidth="true" max="11" min="11" width="10.77734375"/>
+    <col bestFit="true" customWidth="true" max="12" min="12" width="11.88671875"/>
+    <col bestFit="true" customWidth="true" max="13" min="13" width="5.88671875"/>
+    <col bestFit="true" customWidth="true" max="14" min="14" width="7.6640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>302</v>
       </c>
@@ -1893,16 +3837,40 @@
         <v>303</v>
       </c>
       <c r="D2" t="s">
-        <v>304</v>
+        <v>590</v>
       </c>
       <c r="E2" t="s">
-        <v>305</v>
+        <v>591</v>
       </c>
       <c r="F2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>592</v>
+      </c>
+      <c r="G2" t="s">
+        <v>358</v>
+      </c>
+      <c r="H2" t="s">
+        <v>358</v>
+      </c>
+      <c r="I2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J2" t="s">
+        <v>358</v>
+      </c>
+      <c r="K2" t="s">
+        <v>358</v>
+      </c>
+      <c r="L2" t="s">
+        <v>358</v>
+      </c>
+      <c r="M2" t="s">
+        <v>358</v>
+      </c>
+      <c r="N2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>307</v>
       </c>
@@ -1913,16 +3881,40 @@
         <v>308</v>
       </c>
       <c r="D3" t="s">
-        <v>304</v>
+        <v>593</v>
       </c>
       <c r="E3" t="s">
-        <v>309</v>
+        <v>594</v>
       </c>
       <c r="F3" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+        <v>595</v>
+      </c>
+      <c r="G3" t="s">
+        <v>358</v>
+      </c>
+      <c r="H3" t="s">
+        <v>358</v>
+      </c>
+      <c r="I3" t="s">
+        <v>358</v>
+      </c>
+      <c r="J3" t="s">
+        <v>358</v>
+      </c>
+      <c r="K3" t="s">
+        <v>358</v>
+      </c>
+      <c r="L3" t="s">
+        <v>358</v>
+      </c>
+      <c r="M3" t="s">
+        <v>358</v>
+      </c>
+      <c r="N3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>311</v>
       </c>
@@ -1933,16 +3925,40 @@
         <v>312</v>
       </c>
       <c r="D4" t="s">
-        <v>313</v>
+        <v>596</v>
       </c>
       <c r="E4" t="s">
-        <v>314</v>
+        <v>597</v>
       </c>
       <c r="F4" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+        <v>598</v>
+      </c>
+      <c r="G4" t="s">
+        <v>358</v>
+      </c>
+      <c r="H4" t="s">
+        <v>358</v>
+      </c>
+      <c r="I4" t="s">
+        <v>358</v>
+      </c>
+      <c r="J4" t="s">
+        <v>358</v>
+      </c>
+      <c r="K4" t="s">
+        <v>358</v>
+      </c>
+      <c r="L4" t="s">
+        <v>358</v>
+      </c>
+      <c r="M4" t="s">
+        <v>358</v>
+      </c>
+      <c r="N4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>316</v>
       </c>
@@ -1953,13 +3969,37 @@
         <v>317</v>
       </c>
       <c r="D5" t="s">
-        <v>318</v>
+        <v>599</v>
       </c>
       <c r="E5" t="s">
-        <v>319</v>
+        <v>600</v>
       </c>
       <c r="F5" t="s">
-        <v>320</v>
+        <v>601</v>
+      </c>
+      <c r="G5" t="s">
+        <v>358</v>
+      </c>
+      <c r="H5" t="s">
+        <v>358</v>
+      </c>
+      <c r="I5" t="s">
+        <v>358</v>
+      </c>
+      <c r="J5" t="s">
+        <v>358</v>
+      </c>
+      <c r="K5" t="s">
+        <v>358</v>
+      </c>
+      <c r="L5" t="s">
+        <v>358</v>
+      </c>
+      <c r="M5" t="s">
+        <v>358</v>
+      </c>
+      <c r="N5" t="s">
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -1970,68 +4010,68 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col bestFit="true" customWidth="true" max="1" min="1" width="13.77734375"/>
+    <col bestFit="true" customWidth="true" max="2" min="2" width="6.88671875"/>
+    <col bestFit="true" customWidth="true" max="3" min="3" width="32.44140625"/>
+    <col bestFit="true" customWidth="true" max="4" min="4" width="30.21875"/>
+    <col bestFit="true" customWidth="true" max="5" min="5" width="35.21875"/>
+    <col bestFit="true" customWidth="true" max="6" min="6" width="30.88671875"/>
+    <col bestFit="true" customWidth="true" max="7" min="7" width="11.5546875"/>
+    <col bestFit="true" customWidth="true" max="8" min="8" width="6"/>
+    <col bestFit="true" customWidth="true" max="9" min="9" width="7.44140625"/>
+    <col bestFit="true" customWidth="true" max="11" min="11" width="10.77734375"/>
+    <col bestFit="true" customWidth="true" max="12" min="12" width="11.88671875"/>
+    <col bestFit="true" customWidth="true" max="13" min="13" width="5.88671875"/>
+    <col bestFit="true" customWidth="true" max="14" min="14" width="7.6640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>321</v>
       </c>
@@ -2042,16 +4082,40 @@
         <v>322</v>
       </c>
       <c r="D2" t="s">
-        <v>323</v>
+        <v>602</v>
       </c>
       <c r="E2" t="s">
-        <v>324</v>
+        <v>603</v>
       </c>
       <c r="F2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>604</v>
+      </c>
+      <c r="G2" t="s">
+        <v>358</v>
+      </c>
+      <c r="H2" t="s">
+        <v>358</v>
+      </c>
+      <c r="I2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J2" t="s">
+        <v>358</v>
+      </c>
+      <c r="K2" t="s">
+        <v>358</v>
+      </c>
+      <c r="L2" t="s">
+        <v>358</v>
+      </c>
+      <c r="M2" t="s">
+        <v>358</v>
+      </c>
+      <c r="N2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>326</v>
       </c>
@@ -2062,16 +4126,40 @@
         <v>327</v>
       </c>
       <c r="D3" t="s">
-        <v>328</v>
+        <v>605</v>
       </c>
       <c r="E3" t="s">
-        <v>329</v>
+        <v>606</v>
       </c>
       <c r="F3" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+        <v>607</v>
+      </c>
+      <c r="G3" t="s">
+        <v>358</v>
+      </c>
+      <c r="H3" t="s">
+        <v>358</v>
+      </c>
+      <c r="I3" t="s">
+        <v>358</v>
+      </c>
+      <c r="J3" t="s">
+        <v>358</v>
+      </c>
+      <c r="K3" t="s">
+        <v>358</v>
+      </c>
+      <c r="L3" t="s">
+        <v>358</v>
+      </c>
+      <c r="M3" t="s">
+        <v>358</v>
+      </c>
+      <c r="N3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>331</v>
       </c>
@@ -2082,16 +4170,40 @@
         <v>332</v>
       </c>
       <c r="D4" t="s">
-        <v>333</v>
+        <v>608</v>
       </c>
       <c r="E4" t="s">
-        <v>334</v>
+        <v>609</v>
       </c>
       <c r="F4" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+        <v>610</v>
+      </c>
+      <c r="G4" t="s">
+        <v>358</v>
+      </c>
+      <c r="H4" t="s">
+        <v>358</v>
+      </c>
+      <c r="I4" t="s">
+        <v>358</v>
+      </c>
+      <c r="J4" t="s">
+        <v>358</v>
+      </c>
+      <c r="K4" t="s">
+        <v>358</v>
+      </c>
+      <c r="L4" t="s">
+        <v>358</v>
+      </c>
+      <c r="M4" t="s">
+        <v>358</v>
+      </c>
+      <c r="N4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>336</v>
       </c>
@@ -2102,16 +4214,40 @@
         <v>337</v>
       </c>
       <c r="D5" t="s">
-        <v>333</v>
+        <v>611</v>
       </c>
       <c r="E5" t="s">
-        <v>338</v>
+        <v>612</v>
       </c>
       <c r="F5" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+        <v>613</v>
+      </c>
+      <c r="G5" t="s">
+        <v>358</v>
+      </c>
+      <c r="H5" t="s">
+        <v>358</v>
+      </c>
+      <c r="I5" t="s">
+        <v>358</v>
+      </c>
+      <c r="J5" t="s">
+        <v>358</v>
+      </c>
+      <c r="K5" t="s">
+        <v>358</v>
+      </c>
+      <c r="L5" t="s">
+        <v>358</v>
+      </c>
+      <c r="M5" t="s">
+        <v>358</v>
+      </c>
+      <c r="N5" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>340</v>
       </c>
@@ -2122,16 +4258,40 @@
         <v>341</v>
       </c>
       <c r="D6" t="s">
-        <v>333</v>
+        <v>614</v>
       </c>
       <c r="E6" t="s">
-        <v>342</v>
+        <v>615</v>
       </c>
       <c r="F6" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+        <v>616</v>
+      </c>
+      <c r="G6" t="s">
+        <v>358</v>
+      </c>
+      <c r="H6" t="s">
+        <v>358</v>
+      </c>
+      <c r="I6" t="s">
+        <v>358</v>
+      </c>
+      <c r="J6" t="s">
+        <v>358</v>
+      </c>
+      <c r="K6" t="s">
+        <v>358</v>
+      </c>
+      <c r="L6" t="s">
+        <v>358</v>
+      </c>
+      <c r="M6" t="s">
+        <v>358</v>
+      </c>
+      <c r="N6" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>344</v>
       </c>
@@ -2142,16 +4302,40 @@
         <v>345</v>
       </c>
       <c r="D7" t="s">
-        <v>333</v>
+        <v>617</v>
       </c>
       <c r="E7" t="s">
-        <v>346</v>
+        <v>618</v>
       </c>
       <c r="F7" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+        <v>619</v>
+      </c>
+      <c r="G7" t="s">
+        <v>358</v>
+      </c>
+      <c r="H7" t="s">
+        <v>358</v>
+      </c>
+      <c r="I7" t="s">
+        <v>358</v>
+      </c>
+      <c r="J7" t="s">
+        <v>358</v>
+      </c>
+      <c r="K7" t="s">
+        <v>358</v>
+      </c>
+      <c r="L7" t="s">
+        <v>358</v>
+      </c>
+      <c r="M7" t="s">
+        <v>358</v>
+      </c>
+      <c r="N7" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>348</v>
       </c>
@@ -2162,13 +4346,37 @@
         <v>349</v>
       </c>
       <c r="D8" t="s">
-        <v>350</v>
+        <v>522</v>
       </c>
       <c r="E8" t="s">
-        <v>351</v>
+        <v>620</v>
       </c>
       <c r="F8" t="s">
-        <v>352</v>
+        <v>621</v>
+      </c>
+      <c r="G8" t="s">
+        <v>358</v>
+      </c>
+      <c r="H8" t="s">
+        <v>358</v>
+      </c>
+      <c r="I8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K8" t="s">
+        <v>358</v>
+      </c>
+      <c r="L8" t="s">
+        <v>358</v>
+      </c>
+      <c r="M8" t="s">
+        <v>358</v>
+      </c>
+      <c r="N8" t="s">
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -2179,68 +4387,68 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col bestFit="true" customWidth="true" max="1" min="1" width="14"/>
+    <col bestFit="true" customWidth="true" max="2" min="2" width="6.88671875"/>
+    <col bestFit="true" customWidth="true" max="3" min="3" width="24.77734375"/>
+    <col bestFit="true" customWidth="true" max="4" min="4" width="21.88671875"/>
+    <col bestFit="true" customWidth="true" max="5" min="5" width="34.88671875"/>
+    <col bestFit="true" customWidth="true" max="6" min="6" width="24"/>
+    <col bestFit="true" customWidth="true" max="7" min="7" width="11.5546875"/>
+    <col bestFit="true" customWidth="true" max="8" min="8" width="6"/>
+    <col bestFit="true" customWidth="true" max="9" min="9" width="7.44140625"/>
+    <col bestFit="true" customWidth="true" max="11" min="11" width="10.77734375"/>
+    <col bestFit="true" customWidth="true" max="12" min="12" width="11.88671875"/>
+    <col bestFit="true" customWidth="true" max="13" min="13" width="5.88671875"/>
+    <col bestFit="true" customWidth="true" max="14" min="14" width="7.6640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>49</v>
       </c>
@@ -2251,16 +4459,40 @@
         <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>622</v>
       </c>
       <c r="E2" t="s">
-        <v>52</v>
+        <v>623</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>624</v>
+      </c>
+      <c r="G2" t="s">
+        <v>358</v>
+      </c>
+      <c r="H2" t="s">
+        <v>358</v>
+      </c>
+      <c r="I2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J2" t="s">
+        <v>358</v>
+      </c>
+      <c r="K2" t="s">
+        <v>358</v>
+      </c>
+      <c r="L2" t="s">
+        <v>358</v>
+      </c>
+      <c r="M2" t="s">
+        <v>358</v>
+      </c>
+      <c r="N2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>54</v>
       </c>
@@ -2271,16 +4503,40 @@
         <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>625</v>
       </c>
       <c r="E3" t="s">
-        <v>57</v>
+        <v>626</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+        <v>627</v>
+      </c>
+      <c r="G3" t="s">
+        <v>358</v>
+      </c>
+      <c r="H3" t="s">
+        <v>358</v>
+      </c>
+      <c r="I3" t="s">
+        <v>358</v>
+      </c>
+      <c r="J3" t="s">
+        <v>358</v>
+      </c>
+      <c r="K3" t="s">
+        <v>358</v>
+      </c>
+      <c r="L3" t="s">
+        <v>358</v>
+      </c>
+      <c r="M3" t="s">
+        <v>358</v>
+      </c>
+      <c r="N3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>59</v>
       </c>
@@ -2291,13 +4547,37 @@
         <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>628</v>
       </c>
       <c r="E4" t="s">
-        <v>63</v>
+        <v>629</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>630</v>
+      </c>
+      <c r="G4" t="s">
+        <v>358</v>
+      </c>
+      <c r="H4" t="s">
+        <v>358</v>
+      </c>
+      <c r="I4" t="s">
+        <v>358</v>
+      </c>
+      <c r="J4" t="s">
+        <v>358</v>
+      </c>
+      <c r="K4" t="s">
+        <v>358</v>
+      </c>
+      <c r="L4" t="s">
+        <v>358</v>
+      </c>
+      <c r="M4" t="s">
+        <v>358</v>
+      </c>
+      <c r="N4" t="s">
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -2308,68 +4588,68 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:N7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col bestFit="true" customWidth="true" max="1" min="1" width="14.109375"/>
+    <col bestFit="true" customWidth="true" max="2" min="2" width="6.88671875"/>
+    <col bestFit="true" customWidth="true" max="3" min="3" width="23.33203125"/>
+    <col bestFit="true" customWidth="true" max="4" min="4" width="21.88671875"/>
+    <col bestFit="true" customWidth="true" max="5" min="5" width="26.77734375"/>
+    <col bestFit="true" customWidth="true" max="6" min="6" width="29.33203125"/>
+    <col bestFit="true" customWidth="true" max="7" min="7" width="11.5546875"/>
+    <col bestFit="true" customWidth="true" max="8" min="8" width="6"/>
+    <col bestFit="true" customWidth="true" max="9" min="9" width="7.44140625"/>
+    <col bestFit="true" customWidth="true" max="11" min="11" width="10.77734375"/>
+    <col bestFit="true" customWidth="true" max="12" min="12" width="11.88671875"/>
+    <col bestFit="true" customWidth="true" max="13" min="13" width="5.88671875"/>
+    <col bestFit="true" customWidth="true" max="14" min="14" width="7.6640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>65</v>
       </c>
@@ -2380,16 +4660,40 @@
         <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>631</v>
       </c>
       <c r="E2" t="s">
-        <v>68</v>
+        <v>632</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>633</v>
+      </c>
+      <c r="G2" t="s">
+        <v>358</v>
+      </c>
+      <c r="H2" t="s">
+        <v>358</v>
+      </c>
+      <c r="I2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J2" t="s">
+        <v>358</v>
+      </c>
+      <c r="K2" t="s">
+        <v>358</v>
+      </c>
+      <c r="L2" t="s">
+        <v>358</v>
+      </c>
+      <c r="M2" t="s">
+        <v>358</v>
+      </c>
+      <c r="N2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>70</v>
       </c>
@@ -2400,16 +4704,40 @@
         <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>614</v>
       </c>
       <c r="E3" t="s">
-        <v>73</v>
+        <v>634</v>
       </c>
       <c r="F3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+        <v>635</v>
+      </c>
+      <c r="G3" t="s">
+        <v>358</v>
+      </c>
+      <c r="H3" t="s">
+        <v>358</v>
+      </c>
+      <c r="I3" t="s">
+        <v>358</v>
+      </c>
+      <c r="J3" t="s">
+        <v>358</v>
+      </c>
+      <c r="K3" t="s">
+        <v>358</v>
+      </c>
+      <c r="L3" t="s">
+        <v>358</v>
+      </c>
+      <c r="M3" t="s">
+        <v>358</v>
+      </c>
+      <c r="N3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>75</v>
       </c>
@@ -2420,16 +4748,40 @@
         <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>636</v>
       </c>
       <c r="E4" t="s">
-        <v>78</v>
+        <v>637</v>
       </c>
       <c r="F4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+        <v>638</v>
+      </c>
+      <c r="G4" t="s">
+        <v>358</v>
+      </c>
+      <c r="H4" t="s">
+        <v>358</v>
+      </c>
+      <c r="I4" t="s">
+        <v>358</v>
+      </c>
+      <c r="J4" t="s">
+        <v>358</v>
+      </c>
+      <c r="K4" t="s">
+        <v>358</v>
+      </c>
+      <c r="L4" t="s">
+        <v>358</v>
+      </c>
+      <c r="M4" t="s">
+        <v>358</v>
+      </c>
+      <c r="N4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>80</v>
       </c>
@@ -2440,16 +4792,40 @@
         <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>639</v>
       </c>
       <c r="E5" t="s">
-        <v>83</v>
+        <v>640</v>
       </c>
       <c r="F5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+        <v>641</v>
+      </c>
+      <c r="G5" t="s">
+        <v>358</v>
+      </c>
+      <c r="H5" t="s">
+        <v>358</v>
+      </c>
+      <c r="I5" t="s">
+        <v>358</v>
+      </c>
+      <c r="J5" t="s">
+        <v>358</v>
+      </c>
+      <c r="K5" t="s">
+        <v>358</v>
+      </c>
+      <c r="L5" t="s">
+        <v>358</v>
+      </c>
+      <c r="M5" t="s">
+        <v>358</v>
+      </c>
+      <c r="N5" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>85</v>
       </c>
@@ -2460,16 +4836,40 @@
         <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>642</v>
       </c>
       <c r="E6" t="s">
-        <v>87</v>
+        <v>643</v>
       </c>
       <c r="F6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+        <v>644</v>
+      </c>
+      <c r="G6" t="s">
+        <v>358</v>
+      </c>
+      <c r="H6" t="s">
+        <v>358</v>
+      </c>
+      <c r="I6" t="s">
+        <v>358</v>
+      </c>
+      <c r="J6" t="s">
+        <v>358</v>
+      </c>
+      <c r="K6" t="s">
+        <v>358</v>
+      </c>
+      <c r="L6" t="s">
+        <v>358</v>
+      </c>
+      <c r="M6" t="s">
+        <v>358</v>
+      </c>
+      <c r="N6" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>89</v>
       </c>
@@ -2480,13 +4880,37 @@
         <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>645</v>
       </c>
       <c r="E7" t="s">
-        <v>92</v>
+        <v>646</v>
       </c>
       <c r="F7" t="s">
-        <v>93</v>
+        <v>647</v>
+      </c>
+      <c r="G7" t="s">
+        <v>358</v>
+      </c>
+      <c r="H7" t="s">
+        <v>358</v>
+      </c>
+      <c r="I7" t="s">
+        <v>358</v>
+      </c>
+      <c r="J7" t="s">
+        <v>358</v>
+      </c>
+      <c r="K7" t="s">
+        <v>358</v>
+      </c>
+      <c r="L7" t="s">
+        <v>358</v>
+      </c>
+      <c r="M7" t="s">
+        <v>358</v>
+      </c>
+      <c r="N7" t="s">
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -2497,68 +4921,68 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col bestFit="true" customWidth="true" max="1" min="1" width="14.44140625"/>
+    <col bestFit="true" customWidth="true" max="2" min="2" width="6.88671875"/>
+    <col bestFit="true" customWidth="true" max="3" min="3" width="29.21875"/>
+    <col bestFit="true" customWidth="true" max="4" min="4" width="29.33203125"/>
+    <col bestFit="true" customWidth="true" max="5" min="5" width="35.6640625"/>
+    <col bestFit="true" customWidth="true" max="6" min="6" width="37.109375"/>
+    <col bestFit="true" customWidth="true" max="7" min="7" width="11.5546875"/>
+    <col bestFit="true" customWidth="true" max="8" min="8" width="6"/>
+    <col bestFit="true" customWidth="true" max="9" min="9" width="7.44140625"/>
+    <col bestFit="true" customWidth="true" max="11" min="11" width="10.77734375"/>
+    <col bestFit="true" customWidth="true" max="12" min="12" width="11.88671875"/>
+    <col bestFit="true" customWidth="true" max="13" min="13" width="5.88671875"/>
+    <col bestFit="true" customWidth="true" max="14" min="14" width="7.6640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>94</v>
       </c>
@@ -2569,16 +4993,40 @@
         <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>425</v>
       </c>
       <c r="E2" t="s">
-        <v>96</v>
+        <v>426</v>
       </c>
       <c r="F2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>427</v>
+      </c>
+      <c r="G2" t="s">
+        <v>358</v>
+      </c>
+      <c r="H2" t="s">
+        <v>358</v>
+      </c>
+      <c r="I2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J2" t="s">
+        <v>358</v>
+      </c>
+      <c r="K2" t="s">
+        <v>358</v>
+      </c>
+      <c r="L2" t="s">
+        <v>358</v>
+      </c>
+      <c r="M2" t="s">
+        <v>358</v>
+      </c>
+      <c r="N2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>98</v>
       </c>
@@ -2589,16 +5037,40 @@
         <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>428</v>
       </c>
       <c r="E3" t="s">
-        <v>101</v>
+        <v>429</v>
       </c>
       <c r="F3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+        <v>430</v>
+      </c>
+      <c r="G3" t="s">
+        <v>358</v>
+      </c>
+      <c r="H3" t="s">
+        <v>358</v>
+      </c>
+      <c r="I3" t="s">
+        <v>358</v>
+      </c>
+      <c r="J3" t="s">
+        <v>358</v>
+      </c>
+      <c r="K3" t="s">
+        <v>358</v>
+      </c>
+      <c r="L3" t="s">
+        <v>358</v>
+      </c>
+      <c r="M3" t="s">
+        <v>358</v>
+      </c>
+      <c r="N3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>103</v>
       </c>
@@ -2609,16 +5081,40 @@
         <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>431</v>
       </c>
       <c r="E4" t="s">
-        <v>105</v>
+        <v>432</v>
       </c>
       <c r="F4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+        <v>433</v>
+      </c>
+      <c r="G4" t="s">
+        <v>358</v>
+      </c>
+      <c r="H4" t="s">
+        <v>358</v>
+      </c>
+      <c r="I4" t="s">
+        <v>358</v>
+      </c>
+      <c r="J4" t="s">
+        <v>358</v>
+      </c>
+      <c r="K4" t="s">
+        <v>358</v>
+      </c>
+      <c r="L4" t="s">
+        <v>358</v>
+      </c>
+      <c r="M4" t="s">
+        <v>358</v>
+      </c>
+      <c r="N4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>107</v>
       </c>
@@ -2629,16 +5125,40 @@
         <v>108</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>434</v>
       </c>
       <c r="E5" t="s">
-        <v>110</v>
+        <v>435</v>
       </c>
       <c r="F5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+        <v>436</v>
+      </c>
+      <c r="G5" t="s">
+        <v>358</v>
+      </c>
+      <c r="H5" t="s">
+        <v>358</v>
+      </c>
+      <c r="I5" t="s">
+        <v>358</v>
+      </c>
+      <c r="J5" t="s">
+        <v>358</v>
+      </c>
+      <c r="K5" t="s">
+        <v>358</v>
+      </c>
+      <c r="L5" t="s">
+        <v>358</v>
+      </c>
+      <c r="M5" t="s">
+        <v>358</v>
+      </c>
+      <c r="N5" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>112</v>
       </c>
@@ -2649,16 +5169,40 @@
         <v>113</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>437</v>
       </c>
       <c r="E6" t="s">
-        <v>114</v>
+        <v>438</v>
       </c>
       <c r="F6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+        <v>439</v>
+      </c>
+      <c r="G6" t="s">
+        <v>358</v>
+      </c>
+      <c r="H6" t="s">
+        <v>358</v>
+      </c>
+      <c r="I6" t="s">
+        <v>358</v>
+      </c>
+      <c r="J6" t="s">
+        <v>358</v>
+      </c>
+      <c r="K6" t="s">
+        <v>358</v>
+      </c>
+      <c r="L6" t="s">
+        <v>358</v>
+      </c>
+      <c r="M6" t="s">
+        <v>358</v>
+      </c>
+      <c r="N6" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>116</v>
       </c>
@@ -2669,16 +5213,40 @@
         <v>117</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>440</v>
       </c>
       <c r="E7" t="s">
-        <v>114</v>
+        <v>441</v>
       </c>
       <c r="F7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+      <c r="G7" t="s">
+        <v>358</v>
+      </c>
+      <c r="H7" t="s">
+        <v>358</v>
+      </c>
+      <c r="I7" t="s">
+        <v>358</v>
+      </c>
+      <c r="J7" t="s">
+        <v>358</v>
+      </c>
+      <c r="K7" t="s">
+        <v>358</v>
+      </c>
+      <c r="L7" t="s">
+        <v>358</v>
+      </c>
+      <c r="M7" t="s">
+        <v>358</v>
+      </c>
+      <c r="N7" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>120</v>
       </c>
@@ -2689,16 +5257,40 @@
         <v>121</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>443</v>
       </c>
       <c r="E8" t="s">
-        <v>122</v>
+        <v>444</v>
       </c>
       <c r="F8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+      <c r="G8" t="s">
+        <v>358</v>
+      </c>
+      <c r="H8" t="s">
+        <v>358</v>
+      </c>
+      <c r="I8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K8" t="s">
+        <v>358</v>
+      </c>
+      <c r="L8" t="s">
+        <v>358</v>
+      </c>
+      <c r="M8" t="s">
+        <v>358</v>
+      </c>
+      <c r="N8" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
         <v>124</v>
       </c>
@@ -2709,16 +5301,40 @@
         <v>125</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>443</v>
       </c>
       <c r="E9" t="s">
-        <v>126</v>
+        <v>446</v>
       </c>
       <c r="F9" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+        <v>447</v>
+      </c>
+      <c r="G9" t="s">
+        <v>358</v>
+      </c>
+      <c r="H9" t="s">
+        <v>358</v>
+      </c>
+      <c r="I9" t="s">
+        <v>358</v>
+      </c>
+      <c r="J9" t="s">
+        <v>358</v>
+      </c>
+      <c r="K9" t="s">
+        <v>358</v>
+      </c>
+      <c r="L9" t="s">
+        <v>358</v>
+      </c>
+      <c r="M9" t="s">
+        <v>358</v>
+      </c>
+      <c r="N9" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
         <v>128</v>
       </c>
@@ -2729,16 +5345,40 @@
         <v>129</v>
       </c>
       <c r="D10" t="s">
-        <v>118</v>
+        <v>448</v>
       </c>
       <c r="E10" t="s">
-        <v>130</v>
+        <v>449</v>
       </c>
       <c r="F10" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+        <v>450</v>
+      </c>
+      <c r="G10" t="s">
+        <v>358</v>
+      </c>
+      <c r="H10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I10" t="s">
+        <v>358</v>
+      </c>
+      <c r="J10" t="s">
+        <v>358</v>
+      </c>
+      <c r="K10" t="s">
+        <v>358</v>
+      </c>
+      <c r="L10" t="s">
+        <v>358</v>
+      </c>
+      <c r="M10" t="s">
+        <v>358</v>
+      </c>
+      <c r="N10" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
         <v>132</v>
       </c>
@@ -2749,16 +5389,40 @@
         <v>133</v>
       </c>
       <c r="D11" t="s">
-        <v>134</v>
+        <v>451</v>
       </c>
       <c r="E11" t="s">
-        <v>135</v>
+        <v>452</v>
       </c>
       <c r="F11" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+        <v>453</v>
+      </c>
+      <c r="G11" t="s">
+        <v>358</v>
+      </c>
+      <c r="H11" t="s">
+        <v>358</v>
+      </c>
+      <c r="I11" t="s">
+        <v>358</v>
+      </c>
+      <c r="J11" t="s">
+        <v>358</v>
+      </c>
+      <c r="K11" t="s">
+        <v>358</v>
+      </c>
+      <c r="L11" t="s">
+        <v>358</v>
+      </c>
+      <c r="M11" t="s">
+        <v>358</v>
+      </c>
+      <c r="N11" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
         <v>137</v>
       </c>
@@ -2769,16 +5433,40 @@
         <v>138</v>
       </c>
       <c r="D12" t="s">
-        <v>139</v>
+        <v>454</v>
       </c>
       <c r="E12" t="s">
-        <v>140</v>
+        <v>455</v>
       </c>
       <c r="F12" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+        <v>456</v>
+      </c>
+      <c r="G12" t="s">
+        <v>358</v>
+      </c>
+      <c r="H12" t="s">
+        <v>358</v>
+      </c>
+      <c r="I12" t="s">
+        <v>358</v>
+      </c>
+      <c r="J12" t="s">
+        <v>358</v>
+      </c>
+      <c r="K12" t="s">
+        <v>358</v>
+      </c>
+      <c r="L12" t="s">
+        <v>358</v>
+      </c>
+      <c r="M12" t="s">
+        <v>358</v>
+      </c>
+      <c r="N12" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
         <v>142</v>
       </c>
@@ -2789,13 +5477,37 @@
         <v>143</v>
       </c>
       <c r="D13" t="s">
-        <v>139</v>
+        <v>454</v>
       </c>
       <c r="E13" t="s">
-        <v>144</v>
+        <v>457</v>
       </c>
       <c r="F13" t="s">
-        <v>145</v>
+        <v>458</v>
+      </c>
+      <c r="G13" t="s">
+        <v>358</v>
+      </c>
+      <c r="H13" t="s">
+        <v>358</v>
+      </c>
+      <c r="I13" t="s">
+        <v>358</v>
+      </c>
+      <c r="J13" t="s">
+        <v>358</v>
+      </c>
+      <c r="K13" t="s">
+        <v>358</v>
+      </c>
+      <c r="L13" t="s">
+        <v>358</v>
+      </c>
+      <c r="M13" t="s">
+        <v>358</v>
+      </c>
+      <c r="N13" t="s">
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -2806,68 +5518,68 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col bestFit="true" customWidth="true" max="1" min="1" width="12.6640625"/>
+    <col bestFit="true" customWidth="true" max="2" min="2" width="6.88671875"/>
+    <col bestFit="true" customWidth="true" max="3" min="3" width="24.44140625"/>
+    <col bestFit="true" customWidth="true" max="4" min="4" width="25.5546875"/>
+    <col bestFit="true" customWidth="true" max="5" min="5" width="34.88671875"/>
+    <col bestFit="true" customWidth="true" max="6" min="6" width="26.6640625"/>
+    <col bestFit="true" customWidth="true" max="7" min="7" width="11.5546875"/>
+    <col bestFit="true" customWidth="true" max="8" min="8" width="6"/>
+    <col bestFit="true" customWidth="true" max="9" min="9" width="7.44140625"/>
+    <col bestFit="true" customWidth="true" max="11" min="11" width="10.77734375"/>
+    <col bestFit="true" customWidth="true" max="12" min="12" width="11.88671875"/>
+    <col bestFit="true" customWidth="true" max="13" min="13" width="5.88671875"/>
+    <col bestFit="true" customWidth="true" max="14" min="14" width="7.6640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>146</v>
       </c>
@@ -2878,16 +5590,40 @@
         <v>147</v>
       </c>
       <c r="D2" t="s">
-        <v>148</v>
+        <v>459</v>
       </c>
       <c r="E2" t="s">
-        <v>149</v>
+        <v>460</v>
       </c>
       <c r="F2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>461</v>
+      </c>
+      <c r="G2" t="s">
+        <v>358</v>
+      </c>
+      <c r="H2" t="s">
+        <v>358</v>
+      </c>
+      <c r="I2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J2" t="s">
+        <v>358</v>
+      </c>
+      <c r="K2" t="s">
+        <v>358</v>
+      </c>
+      <c r="L2" t="s">
+        <v>358</v>
+      </c>
+      <c r="M2" t="s">
+        <v>358</v>
+      </c>
+      <c r="N2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>151</v>
       </c>
@@ -2898,16 +5634,40 @@
         <v>152</v>
       </c>
       <c r="D3" t="s">
-        <v>148</v>
+        <v>462</v>
       </c>
       <c r="E3" t="s">
-        <v>153</v>
+        <v>463</v>
       </c>
       <c r="F3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+        <v>464</v>
+      </c>
+      <c r="G3" t="s">
+        <v>358</v>
+      </c>
+      <c r="H3" t="s">
+        <v>358</v>
+      </c>
+      <c r="I3" t="s">
+        <v>358</v>
+      </c>
+      <c r="J3" t="s">
+        <v>358</v>
+      </c>
+      <c r="K3" t="s">
+        <v>358</v>
+      </c>
+      <c r="L3" t="s">
+        <v>358</v>
+      </c>
+      <c r="M3" t="s">
+        <v>358</v>
+      </c>
+      <c r="N3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>155</v>
       </c>
@@ -2918,16 +5678,40 @@
         <v>156</v>
       </c>
       <c r="D4" t="s">
-        <v>148</v>
+        <v>465</v>
       </c>
       <c r="E4" t="s">
-        <v>157</v>
+        <v>466</v>
       </c>
       <c r="F4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+        <v>467</v>
+      </c>
+      <c r="G4" t="s">
+        <v>358</v>
+      </c>
+      <c r="H4" t="s">
+        <v>358</v>
+      </c>
+      <c r="I4" t="s">
+        <v>358</v>
+      </c>
+      <c r="J4" t="s">
+        <v>358</v>
+      </c>
+      <c r="K4" t="s">
+        <v>358</v>
+      </c>
+      <c r="L4" t="s">
+        <v>358</v>
+      </c>
+      <c r="M4" t="s">
+        <v>358</v>
+      </c>
+      <c r="N4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>159</v>
       </c>
@@ -2938,16 +5722,40 @@
         <v>160</v>
       </c>
       <c r="D5" t="s">
-        <v>161</v>
+        <v>468</v>
       </c>
       <c r="E5" t="s">
-        <v>162</v>
+        <v>469</v>
       </c>
       <c r="F5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+        <v>470</v>
+      </c>
+      <c r="G5" t="s">
+        <v>358</v>
+      </c>
+      <c r="H5" t="s">
+        <v>358</v>
+      </c>
+      <c r="I5" t="s">
+        <v>358</v>
+      </c>
+      <c r="J5" t="s">
+        <v>358</v>
+      </c>
+      <c r="K5" t="s">
+        <v>358</v>
+      </c>
+      <c r="L5" t="s">
+        <v>358</v>
+      </c>
+      <c r="M5" t="s">
+        <v>358</v>
+      </c>
+      <c r="N5" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>164</v>
       </c>
@@ -2958,16 +5766,40 @@
         <v>165</v>
       </c>
       <c r="D6" t="s">
-        <v>148</v>
+        <v>471</v>
       </c>
       <c r="E6" t="s">
-        <v>166</v>
+        <v>472</v>
       </c>
       <c r="F6" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+        <v>473</v>
+      </c>
+      <c r="G6" t="s">
+        <v>358</v>
+      </c>
+      <c r="H6" t="s">
+        <v>358</v>
+      </c>
+      <c r="I6" t="s">
+        <v>358</v>
+      </c>
+      <c r="J6" t="s">
+        <v>358</v>
+      </c>
+      <c r="K6" t="s">
+        <v>358</v>
+      </c>
+      <c r="L6" t="s">
+        <v>358</v>
+      </c>
+      <c r="M6" t="s">
+        <v>358</v>
+      </c>
+      <c r="N6" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>168</v>
       </c>
@@ -2978,16 +5810,40 @@
         <v>169</v>
       </c>
       <c r="D7" t="s">
-        <v>148</v>
+        <v>474</v>
       </c>
       <c r="E7" t="s">
-        <v>170</v>
+        <v>475</v>
       </c>
       <c r="F7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+        <v>476</v>
+      </c>
+      <c r="G7" t="s">
+        <v>358</v>
+      </c>
+      <c r="H7" t="s">
+        <v>358</v>
+      </c>
+      <c r="I7" t="s">
+        <v>358</v>
+      </c>
+      <c r="J7" t="s">
+        <v>358</v>
+      </c>
+      <c r="K7" t="s">
+        <v>358</v>
+      </c>
+      <c r="L7" t="s">
+        <v>358</v>
+      </c>
+      <c r="M7" t="s">
+        <v>358</v>
+      </c>
+      <c r="N7" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>171</v>
       </c>
@@ -2998,13 +5854,37 @@
         <v>172</v>
       </c>
       <c r="D8" t="s">
-        <v>148</v>
+        <v>477</v>
       </c>
       <c r="E8" t="s">
-        <v>173</v>
+        <v>478</v>
       </c>
       <c r="F8" t="s">
-        <v>174</v>
+        <v>479</v>
+      </c>
+      <c r="G8" t="s">
+        <v>358</v>
+      </c>
+      <c r="H8" t="s">
+        <v>358</v>
+      </c>
+      <c r="I8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K8" t="s">
+        <v>358</v>
+      </c>
+      <c r="L8" t="s">
+        <v>358</v>
+      </c>
+      <c r="M8" t="s">
+        <v>358</v>
+      </c>
+      <c r="N8" t="s">
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -3015,56 +5895,56 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col bestFit="true" customWidth="true" max="1" min="1" width="14.6640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>175</v>
       </c>
@@ -3075,16 +5955,40 @@
         <v>176</v>
       </c>
       <c r="D2" t="s">
-        <v>177</v>
+        <v>480</v>
       </c>
       <c r="E2" t="s">
-        <v>178</v>
+        <v>481</v>
       </c>
       <c r="F2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>482</v>
+      </c>
+      <c r="G2" t="s">
+        <v>358</v>
+      </c>
+      <c r="H2" t="s">
+        <v>358</v>
+      </c>
+      <c r="I2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J2" t="s">
+        <v>358</v>
+      </c>
+      <c r="K2" t="s">
+        <v>358</v>
+      </c>
+      <c r="L2" t="s">
+        <v>358</v>
+      </c>
+      <c r="M2" t="s">
+        <v>358</v>
+      </c>
+      <c r="N2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>180</v>
       </c>
@@ -3095,16 +5999,40 @@
         <v>181</v>
       </c>
       <c r="D3" t="s">
-        <v>182</v>
+        <v>483</v>
       </c>
       <c r="E3" t="s">
-        <v>183</v>
+        <v>484</v>
       </c>
       <c r="F3" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+        <v>485</v>
+      </c>
+      <c r="G3" t="s">
+        <v>358</v>
+      </c>
+      <c r="H3" t="s">
+        <v>358</v>
+      </c>
+      <c r="I3" t="s">
+        <v>358</v>
+      </c>
+      <c r="J3" t="s">
+        <v>358</v>
+      </c>
+      <c r="K3" t="s">
+        <v>358</v>
+      </c>
+      <c r="L3" t="s">
+        <v>358</v>
+      </c>
+      <c r="M3" t="s">
+        <v>358</v>
+      </c>
+      <c r="N3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>185</v>
       </c>
@@ -3115,16 +6043,40 @@
         <v>186</v>
       </c>
       <c r="D4" t="s">
-        <v>182</v>
+        <v>486</v>
       </c>
       <c r="E4" t="s">
-        <v>187</v>
+        <v>487</v>
       </c>
       <c r="F4" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+        <v>488</v>
+      </c>
+      <c r="G4" t="s">
+        <v>358</v>
+      </c>
+      <c r="H4" t="s">
+        <v>358</v>
+      </c>
+      <c r="I4" t="s">
+        <v>358</v>
+      </c>
+      <c r="J4" t="s">
+        <v>358</v>
+      </c>
+      <c r="K4" t="s">
+        <v>358</v>
+      </c>
+      <c r="L4" t="s">
+        <v>358</v>
+      </c>
+      <c r="M4" t="s">
+        <v>358</v>
+      </c>
+      <c r="N4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>189</v>
       </c>
@@ -3135,13 +6087,37 @@
         <v>190</v>
       </c>
       <c r="D5" t="s">
-        <v>177</v>
+        <v>489</v>
       </c>
       <c r="E5" t="s">
-        <v>191</v>
+        <v>490</v>
       </c>
       <c r="F5" t="s">
-        <v>192</v>
+        <v>491</v>
+      </c>
+      <c r="G5" t="s">
+        <v>358</v>
+      </c>
+      <c r="H5" t="s">
+        <v>358</v>
+      </c>
+      <c r="I5" t="s">
+        <v>358</v>
+      </c>
+      <c r="J5" t="s">
+        <v>358</v>
+      </c>
+      <c r="K5" t="s">
+        <v>358</v>
+      </c>
+      <c r="L5" t="s">
+        <v>358</v>
+      </c>
+      <c r="M5" t="s">
+        <v>358</v>
+      </c>
+      <c r="N5" t="s">
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -3152,68 +6128,68 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:N11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col bestFit="true" customWidth="true" max="1" min="1" width="13.109375"/>
+    <col bestFit="true" customWidth="true" max="2" min="2" width="6.88671875"/>
+    <col bestFit="true" customWidth="true" max="3" min="3" width="31.33203125"/>
+    <col bestFit="true" customWidth="true" max="4" min="4" width="24.6640625"/>
+    <col bestFit="true" customWidth="true" max="5" min="5" width="36.5546875"/>
+    <col bestFit="true" customWidth="true" max="6" min="6" width="31.21875"/>
+    <col bestFit="true" customWidth="true" max="7" min="7" width="11.5546875"/>
+    <col bestFit="true" customWidth="true" max="8" min="8" width="6"/>
+    <col bestFit="true" customWidth="true" max="9" min="9" width="7.44140625"/>
+    <col bestFit="true" customWidth="true" max="11" min="11" width="10.77734375"/>
+    <col bestFit="true" customWidth="true" max="12" min="12" width="11.88671875"/>
+    <col bestFit="true" customWidth="true" max="13" min="13" width="5.88671875"/>
+    <col bestFit="true" customWidth="true" max="14" min="14" width="7.6640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>193</v>
       </c>
@@ -3224,16 +6200,40 @@
         <v>194</v>
       </c>
       <c r="D2" t="s">
-        <v>195</v>
+        <v>492</v>
       </c>
       <c r="E2" t="s">
-        <v>196</v>
+        <v>493</v>
       </c>
       <c r="F2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>494</v>
+      </c>
+      <c r="G2" t="s">
+        <v>358</v>
+      </c>
+      <c r="H2" t="s">
+        <v>358</v>
+      </c>
+      <c r="I2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J2" t="s">
+        <v>358</v>
+      </c>
+      <c r="K2" t="s">
+        <v>358</v>
+      </c>
+      <c r="L2" t="s">
+        <v>358</v>
+      </c>
+      <c r="M2" t="s">
+        <v>358</v>
+      </c>
+      <c r="N2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>198</v>
       </c>
@@ -3244,16 +6244,40 @@
         <v>199</v>
       </c>
       <c r="D3" t="s">
-        <v>200</v>
+        <v>495</v>
       </c>
       <c r="E3" t="s">
-        <v>201</v>
+        <v>496</v>
       </c>
       <c r="F3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+        <v>497</v>
+      </c>
+      <c r="G3" t="s">
+        <v>358</v>
+      </c>
+      <c r="H3" t="s">
+        <v>358</v>
+      </c>
+      <c r="I3" t="s">
+        <v>358</v>
+      </c>
+      <c r="J3" t="s">
+        <v>358</v>
+      </c>
+      <c r="K3" t="s">
+        <v>358</v>
+      </c>
+      <c r="L3" t="s">
+        <v>358</v>
+      </c>
+      <c r="M3" t="s">
+        <v>358</v>
+      </c>
+      <c r="N3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>203</v>
       </c>
@@ -3264,16 +6288,40 @@
         <v>204</v>
       </c>
       <c r="D4" t="s">
-        <v>205</v>
+        <v>498</v>
       </c>
       <c r="E4" t="s">
-        <v>206</v>
+        <v>499</v>
       </c>
       <c r="F4" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+        <v>500</v>
+      </c>
+      <c r="G4" t="s">
+        <v>358</v>
+      </c>
+      <c r="H4" t="s">
+        <v>358</v>
+      </c>
+      <c r="I4" t="s">
+        <v>358</v>
+      </c>
+      <c r="J4" t="s">
+        <v>358</v>
+      </c>
+      <c r="K4" t="s">
+        <v>358</v>
+      </c>
+      <c r="L4" t="s">
+        <v>358</v>
+      </c>
+      <c r="M4" t="s">
+        <v>358</v>
+      </c>
+      <c r="N4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>208</v>
       </c>
@@ -3284,16 +6332,40 @@
         <v>209</v>
       </c>
       <c r="D5" t="s">
-        <v>210</v>
+        <v>501</v>
       </c>
       <c r="E5" t="s">
-        <v>211</v>
+        <v>502</v>
       </c>
       <c r="F5" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+        <v>503</v>
+      </c>
+      <c r="G5" t="s">
+        <v>358</v>
+      </c>
+      <c r="H5" t="s">
+        <v>358</v>
+      </c>
+      <c r="I5" t="s">
+        <v>358</v>
+      </c>
+      <c r="J5" t="s">
+        <v>358</v>
+      </c>
+      <c r="K5" t="s">
+        <v>358</v>
+      </c>
+      <c r="L5" t="s">
+        <v>358</v>
+      </c>
+      <c r="M5" t="s">
+        <v>358</v>
+      </c>
+      <c r="N5" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>213</v>
       </c>
@@ -3304,16 +6376,40 @@
         <v>214</v>
       </c>
       <c r="D6" t="s">
-        <v>215</v>
+        <v>504</v>
       </c>
       <c r="E6" t="s">
-        <v>216</v>
+        <v>505</v>
       </c>
       <c r="F6" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+        <v>506</v>
+      </c>
+      <c r="G6" t="s">
+        <v>358</v>
+      </c>
+      <c r="H6" t="s">
+        <v>358</v>
+      </c>
+      <c r="I6" t="s">
+        <v>358</v>
+      </c>
+      <c r="J6" t="s">
+        <v>358</v>
+      </c>
+      <c r="K6" t="s">
+        <v>358</v>
+      </c>
+      <c r="L6" t="s">
+        <v>358</v>
+      </c>
+      <c r="M6" t="s">
+        <v>358</v>
+      </c>
+      <c r="N6" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>218</v>
       </c>
@@ -3324,16 +6420,40 @@
         <v>219</v>
       </c>
       <c r="D7" t="s">
-        <v>220</v>
+        <v>507</v>
       </c>
       <c r="E7" t="s">
-        <v>221</v>
+        <v>508</v>
       </c>
       <c r="F7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+        <v>509</v>
+      </c>
+      <c r="G7" t="s">
+        <v>358</v>
+      </c>
+      <c r="H7" t="s">
+        <v>358</v>
+      </c>
+      <c r="I7" t="s">
+        <v>358</v>
+      </c>
+      <c r="J7" t="s">
+        <v>358</v>
+      </c>
+      <c r="K7" t="s">
+        <v>358</v>
+      </c>
+      <c r="L7" t="s">
+        <v>358</v>
+      </c>
+      <c r="M7" t="s">
+        <v>358</v>
+      </c>
+      <c r="N7" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>223</v>
       </c>
@@ -3344,16 +6464,40 @@
         <v>224</v>
       </c>
       <c r="D8" t="s">
-        <v>225</v>
+        <v>510</v>
       </c>
       <c r="E8" t="s">
-        <v>226</v>
+        <v>511</v>
       </c>
       <c r="F8" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+        <v>512</v>
+      </c>
+      <c r="G8" t="s">
+        <v>358</v>
+      </c>
+      <c r="H8" t="s">
+        <v>358</v>
+      </c>
+      <c r="I8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K8" t="s">
+        <v>358</v>
+      </c>
+      <c r="L8" t="s">
+        <v>358</v>
+      </c>
+      <c r="M8" t="s">
+        <v>358</v>
+      </c>
+      <c r="N8" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
         <v>228</v>
       </c>
@@ -3364,16 +6508,40 @@
         <v>229</v>
       </c>
       <c r="D9" t="s">
-        <v>230</v>
+        <v>513</v>
       </c>
       <c r="E9" t="s">
-        <v>231</v>
+        <v>514</v>
       </c>
       <c r="F9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+        <v>515</v>
+      </c>
+      <c r="G9" t="s">
+        <v>358</v>
+      </c>
+      <c r="H9" t="s">
+        <v>358</v>
+      </c>
+      <c r="I9" t="s">
+        <v>358</v>
+      </c>
+      <c r="J9" t="s">
+        <v>358</v>
+      </c>
+      <c r="K9" t="s">
+        <v>358</v>
+      </c>
+      <c r="L9" t="s">
+        <v>358</v>
+      </c>
+      <c r="M9" t="s">
+        <v>358</v>
+      </c>
+      <c r="N9" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
         <v>233</v>
       </c>
@@ -3384,16 +6552,40 @@
         <v>234</v>
       </c>
       <c r="D10" t="s">
-        <v>235</v>
+        <v>516</v>
       </c>
       <c r="E10" t="s">
-        <v>236</v>
+        <v>517</v>
       </c>
       <c r="F10" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+        <v>518</v>
+      </c>
+      <c r="G10" t="s">
+        <v>358</v>
+      </c>
+      <c r="H10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I10" t="s">
+        <v>358</v>
+      </c>
+      <c r="J10" t="s">
+        <v>358</v>
+      </c>
+      <c r="K10" t="s">
+        <v>358</v>
+      </c>
+      <c r="L10" t="s">
+        <v>358</v>
+      </c>
+      <c r="M10" t="s">
+        <v>358</v>
+      </c>
+      <c r="N10" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
         <v>238</v>
       </c>
@@ -3404,13 +6596,37 @@
         <v>239</v>
       </c>
       <c r="D11" t="s">
-        <v>240</v>
+        <v>519</v>
       </c>
       <c r="E11" t="s">
-        <v>231</v>
+        <v>520</v>
       </c>
       <c r="F11" t="s">
-        <v>241</v>
+        <v>521</v>
+      </c>
+      <c r="G11" t="s">
+        <v>358</v>
+      </c>
+      <c r="H11" t="s">
+        <v>358</v>
+      </c>
+      <c r="I11" t="s">
+        <v>358</v>
+      </c>
+      <c r="J11" t="s">
+        <v>358</v>
+      </c>
+      <c r="K11" t="s">
+        <v>358</v>
+      </c>
+      <c r="L11" t="s">
+        <v>358</v>
+      </c>
+      <c r="M11" t="s">
+        <v>358</v>
+      </c>
+      <c r="N11" t="s">
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -3421,68 +6637,68 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:N7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col bestFit="true" customWidth="true" max="1" min="1" width="14"/>
+    <col bestFit="true" customWidth="true" max="2" min="2" width="6.88671875"/>
+    <col bestFit="true" customWidth="true" max="3" min="3" width="18.33203125"/>
+    <col bestFit="true" customWidth="true" max="4" min="4" width="20.21875"/>
+    <col bestFit="true" customWidth="true" max="5" min="5" width="24.21875"/>
+    <col bestFit="true" customWidth="true" max="6" min="6" width="28.5546875"/>
+    <col bestFit="true" customWidth="true" max="7" min="7" width="11.5546875"/>
+    <col bestFit="true" customWidth="true" max="8" min="8" width="6"/>
+    <col bestFit="true" customWidth="true" max="9" min="9" width="7.44140625"/>
+    <col bestFit="true" customWidth="true" max="11" min="11" width="10.77734375"/>
+    <col bestFit="true" customWidth="true" max="12" min="12" width="11.88671875"/>
+    <col bestFit="true" customWidth="true" max="13" min="13" width="5.88671875"/>
+    <col bestFit="true" customWidth="true" max="14" min="14" width="7.6640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>242</v>
       </c>
@@ -3493,16 +6709,40 @@
         <v>243</v>
       </c>
       <c r="D2" t="s">
-        <v>244</v>
+        <v>522</v>
       </c>
       <c r="E2" t="s">
-        <v>245</v>
+        <v>523</v>
       </c>
       <c r="F2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>524</v>
+      </c>
+      <c r="G2" t="s">
+        <v>358</v>
+      </c>
+      <c r="H2" t="s">
+        <v>358</v>
+      </c>
+      <c r="I2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J2" t="s">
+        <v>358</v>
+      </c>
+      <c r="K2" t="s">
+        <v>358</v>
+      </c>
+      <c r="L2" t="s">
+        <v>358</v>
+      </c>
+      <c r="M2" t="s">
+        <v>358</v>
+      </c>
+      <c r="N2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>247</v>
       </c>
@@ -3513,16 +6753,40 @@
         <v>248</v>
       </c>
       <c r="D3" t="s">
-        <v>249</v>
+        <v>525</v>
       </c>
       <c r="E3" t="s">
-        <v>250</v>
+        <v>526</v>
       </c>
       <c r="F3" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+        <v>527</v>
+      </c>
+      <c r="G3" t="s">
+        <v>358</v>
+      </c>
+      <c r="H3" t="s">
+        <v>358</v>
+      </c>
+      <c r="I3" t="s">
+        <v>358</v>
+      </c>
+      <c r="J3" t="s">
+        <v>358</v>
+      </c>
+      <c r="K3" t="s">
+        <v>358</v>
+      </c>
+      <c r="L3" t="s">
+        <v>358</v>
+      </c>
+      <c r="M3" t="s">
+        <v>358</v>
+      </c>
+      <c r="N3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>252</v>
       </c>
@@ -3533,16 +6797,40 @@
         <v>253</v>
       </c>
       <c r="D4" t="s">
-        <v>254</v>
+        <v>528</v>
       </c>
       <c r="E4" t="s">
-        <v>255</v>
+        <v>529</v>
       </c>
       <c r="F4" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+        <v>530</v>
+      </c>
+      <c r="G4" t="s">
+        <v>358</v>
+      </c>
+      <c r="H4" t="s">
+        <v>358</v>
+      </c>
+      <c r="I4" t="s">
+        <v>358</v>
+      </c>
+      <c r="J4" t="s">
+        <v>358</v>
+      </c>
+      <c r="K4" t="s">
+        <v>358</v>
+      </c>
+      <c r="L4" t="s">
+        <v>358</v>
+      </c>
+      <c r="M4" t="s">
+        <v>358</v>
+      </c>
+      <c r="N4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>257</v>
       </c>
@@ -3553,16 +6841,40 @@
         <v>258</v>
       </c>
       <c r="D5" t="s">
-        <v>254</v>
+        <v>531</v>
       </c>
       <c r="E5" t="s">
-        <v>259</v>
+        <v>532</v>
       </c>
       <c r="F5" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+        <v>533</v>
+      </c>
+      <c r="G5" t="s">
+        <v>358</v>
+      </c>
+      <c r="H5" t="s">
+        <v>358</v>
+      </c>
+      <c r="I5" t="s">
+        <v>358</v>
+      </c>
+      <c r="J5" t="s">
+        <v>358</v>
+      </c>
+      <c r="K5" t="s">
+        <v>358</v>
+      </c>
+      <c r="L5" t="s">
+        <v>358</v>
+      </c>
+      <c r="M5" t="s">
+        <v>358</v>
+      </c>
+      <c r="N5" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>261</v>
       </c>
@@ -3573,16 +6885,40 @@
         <v>262</v>
       </c>
       <c r="D6" t="s">
-        <v>263</v>
+        <v>525</v>
       </c>
       <c r="E6" t="s">
-        <v>264</v>
+        <v>534</v>
       </c>
       <c r="F6" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+        <v>535</v>
+      </c>
+      <c r="G6" t="s">
+        <v>358</v>
+      </c>
+      <c r="H6" t="s">
+        <v>358</v>
+      </c>
+      <c r="I6" t="s">
+        <v>358</v>
+      </c>
+      <c r="J6" t="s">
+        <v>358</v>
+      </c>
+      <c r="K6" t="s">
+        <v>358</v>
+      </c>
+      <c r="L6" t="s">
+        <v>358</v>
+      </c>
+      <c r="M6" t="s">
+        <v>358</v>
+      </c>
+      <c r="N6" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>266</v>
       </c>
@@ -3593,13 +6929,37 @@
         <v>267</v>
       </c>
       <c r="D7" t="s">
-        <v>268</v>
+        <v>536</v>
       </c>
       <c r="E7" t="s">
-        <v>269</v>
+        <v>537</v>
       </c>
       <c r="F7" t="s">
-        <v>270</v>
+        <v>538</v>
+      </c>
+      <c r="G7" t="s">
+        <v>358</v>
+      </c>
+      <c r="H7" t="s">
+        <v>358</v>
+      </c>
+      <c r="I7" t="s">
+        <v>358</v>
+      </c>
+      <c r="J7" t="s">
+        <v>358</v>
+      </c>
+      <c r="K7" t="s">
+        <v>358</v>
+      </c>
+      <c r="L7" t="s">
+        <v>358</v>
+      </c>
+      <c r="M7" t="s">
+        <v>358</v>
+      </c>
+      <c r="N7" t="s">
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -3628,46 +6988,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3682,13 +7042,37 @@
         <v>272</v>
       </c>
       <c r="D2" t="s">
-        <v>273</v>
+        <v>539</v>
       </c>
       <c r="E2" t="s">
-        <v>274</v>
+        <v>540</v>
       </c>
       <c r="F2" t="s">
-        <v>275</v>
+        <v>541</v>
+      </c>
+      <c r="G2" t="s">
+        <v>358</v>
+      </c>
+      <c r="H2" t="s">
+        <v>358</v>
+      </c>
+      <c r="I2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J2" t="s">
+        <v>358</v>
+      </c>
+      <c r="K2" t="s">
+        <v>358</v>
+      </c>
+      <c r="L2" t="s">
+        <v>358</v>
+      </c>
+      <c r="M2" t="s">
+        <v>358</v>
+      </c>
+      <c r="N2" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -3702,13 +7086,37 @@
         <v>277</v>
       </c>
       <c r="D3" t="s">
-        <v>278</v>
+        <v>542</v>
       </c>
       <c r="E3" t="s">
-        <v>274</v>
+        <v>543</v>
       </c>
       <c r="F3" t="s">
-        <v>279</v>
+        <v>544</v>
+      </c>
+      <c r="G3" t="s">
+        <v>358</v>
+      </c>
+      <c r="H3" t="s">
+        <v>358</v>
+      </c>
+      <c r="I3" t="s">
+        <v>358</v>
+      </c>
+      <c r="J3" t="s">
+        <v>358</v>
+      </c>
+      <c r="K3" t="s">
+        <v>358</v>
+      </c>
+      <c r="L3" t="s">
+        <v>358</v>
+      </c>
+      <c r="M3" t="s">
+        <v>358</v>
+      </c>
+      <c r="N3" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -3722,13 +7130,37 @@
         <v>281</v>
       </c>
       <c r="D4" t="s">
-        <v>282</v>
+        <v>545</v>
       </c>
       <c r="E4" t="s">
-        <v>274</v>
+        <v>546</v>
       </c>
       <c r="F4" t="s">
-        <v>283</v>
+        <v>547</v>
+      </c>
+      <c r="G4" t="s">
+        <v>358</v>
+      </c>
+      <c r="H4" t="s">
+        <v>358</v>
+      </c>
+      <c r="I4" t="s">
+        <v>358</v>
+      </c>
+      <c r="J4" t="s">
+        <v>358</v>
+      </c>
+      <c r="K4" t="s">
+        <v>358</v>
+      </c>
+      <c r="L4" t="s">
+        <v>358</v>
+      </c>
+      <c r="M4" t="s">
+        <v>358</v>
+      </c>
+      <c r="N4" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -3742,13 +7174,37 @@
         <v>285</v>
       </c>
       <c r="D5" t="s">
-        <v>286</v>
+        <v>548</v>
       </c>
       <c r="E5" t="s">
-        <v>274</v>
+        <v>549</v>
       </c>
       <c r="F5" t="s">
-        <v>287</v>
+        <v>550</v>
+      </c>
+      <c r="G5" t="s">
+        <v>358</v>
+      </c>
+      <c r="H5" t="s">
+        <v>358</v>
+      </c>
+      <c r="I5" t="s">
+        <v>358</v>
+      </c>
+      <c r="J5" t="s">
+        <v>358</v>
+      </c>
+      <c r="K5" t="s">
+        <v>358</v>
+      </c>
+      <c r="L5" t="s">
+        <v>358</v>
+      </c>
+      <c r="M5" t="s">
+        <v>358</v>
+      </c>
+      <c r="N5" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -3762,13 +7218,37 @@
         <v>289</v>
       </c>
       <c r="D6" t="s">
-        <v>290</v>
+        <v>551</v>
       </c>
       <c r="E6" t="s">
-        <v>291</v>
+        <v>552</v>
       </c>
       <c r="F6" t="s">
-        <v>292</v>
+        <v>553</v>
+      </c>
+      <c r="G6" t="s">
+        <v>358</v>
+      </c>
+      <c r="H6" t="s">
+        <v>358</v>
+      </c>
+      <c r="I6" t="s">
+        <v>358</v>
+      </c>
+      <c r="J6" t="s">
+        <v>358</v>
+      </c>
+      <c r="K6" t="s">
+        <v>358</v>
+      </c>
+      <c r="L6" t="s">
+        <v>358</v>
+      </c>
+      <c r="M6" t="s">
+        <v>358</v>
+      </c>
+      <c r="N6" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -3782,13 +7262,37 @@
         <v>294</v>
       </c>
       <c r="D7" t="s">
-        <v>278</v>
+        <v>554</v>
       </c>
       <c r="E7" t="s">
-        <v>295</v>
+        <v>555</v>
       </c>
       <c r="F7" t="s">
-        <v>296</v>
+        <v>556</v>
+      </c>
+      <c r="G7" t="s">
+        <v>358</v>
+      </c>
+      <c r="H7" t="s">
+        <v>358</v>
+      </c>
+      <c r="I7" t="s">
+        <v>358</v>
+      </c>
+      <c r="J7" t="s">
+        <v>358</v>
+      </c>
+      <c r="K7" t="s">
+        <v>358</v>
+      </c>
+      <c r="L7" t="s">
+        <v>358</v>
+      </c>
+      <c r="M7" t="s">
+        <v>358</v>
+      </c>
+      <c r="N7" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -3802,13 +7306,37 @@
         <v>298</v>
       </c>
       <c r="D8" t="s">
-        <v>299</v>
+        <v>557</v>
       </c>
       <c r="E8" t="s">
-        <v>300</v>
+        <v>558</v>
       </c>
       <c r="F8" t="s">
-        <v>301</v>
+        <v>559</v>
+      </c>
+      <c r="G8" t="s">
+        <v>358</v>
+      </c>
+      <c r="H8" t="s">
+        <v>358</v>
+      </c>
+      <c r="I8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J8" t="s">
+        <v>358</v>
+      </c>
+      <c r="K8" t="s">
+        <v>358</v>
+      </c>
+      <c r="L8" t="s">
+        <v>358</v>
+      </c>
+      <c r="M8" t="s">
+        <v>358</v>
+      </c>
+      <c r="N8" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="9">
@@ -3822,13 +7350,13 @@
         <v>354</v>
       </c>
       <c r="D9" t="s">
-        <v>355</v>
+        <v>560</v>
       </c>
       <c r="E9" t="s">
-        <v>356</v>
+        <v>561</v>
       </c>
       <c r="F9" t="s">
-        <v>357</v>
+        <v>562</v>
       </c>
       <c r="G9" t="s">
         <v>358</v>
@@ -3866,13 +7394,13 @@
         <v>360</v>
       </c>
       <c r="D10" t="s">
-        <v>361</v>
+        <v>563</v>
       </c>
       <c r="E10" t="s">
-        <v>362</v>
+        <v>564</v>
       </c>
       <c r="F10" t="s">
-        <v>363</v>
+        <v>565</v>
       </c>
       <c r="G10" t="s">
         <v>358</v>
@@ -3910,13 +7438,13 @@
         <v>365</v>
       </c>
       <c r="D11" t="s">
-        <v>366</v>
+        <v>566</v>
       </c>
       <c r="E11" t="s">
-        <v>367</v>
+        <v>567</v>
       </c>
       <c r="F11" t="s">
-        <v>368</v>
+        <v>568</v>
       </c>
       <c r="G11" t="s">
         <v>358</v>
@@ -3954,13 +7482,13 @@
         <v>370</v>
       </c>
       <c r="D12" t="s">
-        <v>371</v>
+        <v>569</v>
       </c>
       <c r="E12" t="s">
-        <v>372</v>
+        <v>570</v>
       </c>
       <c r="F12" t="s">
-        <v>373</v>
+        <v>571</v>
       </c>
       <c r="G12" t="s">
         <v>358</v>
@@ -3998,13 +7526,13 @@
         <v>375</v>
       </c>
       <c r="D13" t="s">
-        <v>376</v>
+        <v>572</v>
       </c>
       <c r="E13" t="s">
-        <v>377</v>
+        <v>573</v>
       </c>
       <c r="F13" t="s">
-        <v>378</v>
+        <v>574</v>
       </c>
       <c r="G13" t="s">
         <v>358</v>
@@ -4042,13 +7570,13 @@
         <v>380</v>
       </c>
       <c r="D14" t="s">
-        <v>381</v>
+        <v>575</v>
       </c>
       <c r="E14" t="s">
-        <v>382</v>
+        <v>576</v>
       </c>
       <c r="F14" t="s">
-        <v>383</v>
+        <v>577</v>
       </c>
       <c r="G14" t="s">
         <v>358</v>
@@ -4086,13 +7614,13 @@
         <v>385</v>
       </c>
       <c r="D15" t="s">
-        <v>386</v>
+        <v>578</v>
       </c>
       <c r="E15" t="s">
-        <v>387</v>
+        <v>579</v>
       </c>
       <c r="F15" t="s">
-        <v>388</v>
+        <v>580</v>
       </c>
       <c r="G15" t="s">
         <v>358</v>
@@ -4130,13 +7658,13 @@
         <v>390</v>
       </c>
       <c r="D16" t="s">
-        <v>391</v>
+        <v>581</v>
       </c>
       <c r="E16" t="s">
-        <v>392</v>
+        <v>582</v>
       </c>
       <c r="F16" t="s">
-        <v>393</v>
+        <v>583</v>
       </c>
       <c r="G16" t="s">
         <v>358</v>
@@ -4174,13 +7702,13 @@
         <v>395</v>
       </c>
       <c r="D17" t="s">
-        <v>396</v>
+        <v>584</v>
       </c>
       <c r="E17" t="s">
-        <v>397</v>
+        <v>585</v>
       </c>
       <c r="F17" t="s">
-        <v>398</v>
+        <v>586</v>
       </c>
       <c r="G17" t="s">
         <v>358</v>
@@ -4218,13 +7746,13 @@
         <v>400</v>
       </c>
       <c r="D18" t="s">
-        <v>401</v>
+        <v>587</v>
       </c>
       <c r="E18" t="s">
-        <v>402</v>
+        <v>588</v>
       </c>
       <c r="F18" t="s">
-        <v>403</v>
+        <v>589</v>
       </c>
       <c r="G18" t="s">
         <v>358</v>
